--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A02A6E-3EA1-4A49-824E-4089E755E118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E83917B-D310-4E97-B2F8-927DC46C70EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="8" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="1" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -13207,6 +13207,7 @@
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -13271,7 +13272,7 @@
       </c>
       <c r="B2">
         <f>SUM(C2:R2)</f>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -13280,6 +13281,45 @@
         <v>1</v>
       </c>
       <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
         <v>1</v>
       </c>
     </row>
@@ -13289,7 +13329,7 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B14" si="0">SUM(C3:R3)</f>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -13298,6 +13338,45 @@
         <v>1</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
         <v>1</v>
       </c>
     </row>
@@ -13307,7 +13386,7 @@
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -13316,6 +13395,45 @@
         <v>1</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
         <v>1</v>
       </c>
     </row>
@@ -13325,7 +13443,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -13334,6 +13452,45 @@
         <v>1</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
         <v>1</v>
       </c>
     </row>
@@ -13343,7 +13500,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -13352,6 +13509,45 @@
         <v>1</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
         <v>1</v>
       </c>
     </row>
@@ -13361,7 +13557,7 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -13370,6 +13566,45 @@
         <v>1</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
         <v>1</v>
       </c>
     </row>
@@ -13379,7 +13614,7 @@
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -13388,6 +13623,45 @@
         <v>1</v>
       </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
         <v>1</v>
       </c>
     </row>
@@ -13397,7 +13671,7 @@
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -13406,6 +13680,45 @@
         <v>1</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
         <v>1</v>
       </c>
     </row>
@@ -13415,7 +13728,7 @@
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -13424,6 +13737,45 @@
         <v>1</v>
       </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
         <v>1</v>
       </c>
     </row>
@@ -13433,7 +13785,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -13442,6 +13794,45 @@
         <v>1</v>
       </c>
       <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
         <v>1</v>
       </c>
     </row>
@@ -13451,7 +13842,7 @@
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -13460,6 +13851,45 @@
         <v>1</v>
       </c>
       <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
         <v>1</v>
       </c>
     </row>
@@ -13469,7 +13899,7 @@
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -13479,6 +13909,45 @@
       </c>
       <c r="E13">
         <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -13487,7 +13956,7 @@
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -13496,6 +13965,45 @@
         <v>1</v>
       </c>
       <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
         <v>1</v>
       </c>
     </row>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E83917B-D310-4E97-B2F8-927DC46C70EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="1" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="1" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E83917B-D310-4E97-B2F8-927DC46C70EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCF17F8-9A94-4DD9-8AD7-5B5DF04802D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="1" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1725,6 +1725,12 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AD2">
+        <v>9</v>
+      </c>
+      <c r="AE2">
+        <v>16</v>
+      </c>
       <c r="AF2">
         <v>17</v>
       </c>
@@ -1751,6 +1757,12 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AD3">
+        <v>16</v>
+      </c>
+      <c r="AE3">
+        <v>15</v>
+      </c>
       <c r="AF3">
         <v>17</v>
       </c>
@@ -1778,8 +1790,12 @@
         <v>3</v>
       </c>
       <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
+      <c r="AD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0</v>
+      </c>
       <c r="AF4" s="1">
         <v>0</v>
       </c>
@@ -1806,6 +1822,12 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AD5">
+        <v>16</v>
+      </c>
+      <c r="AE5">
+        <v>16</v>
+      </c>
       <c r="AF5">
         <v>17</v>
       </c>
@@ -1833,8 +1855,12 @@
         <v>5</v>
       </c>
       <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
       <c r="AF6" s="1">
         <v>0</v>
       </c>
@@ -1861,6 +1887,12 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AD7">
+        <v>16</v>
+      </c>
+      <c r="AE7">
+        <v>16</v>
+      </c>
       <c r="AF7">
         <v>17</v>
       </c>
@@ -1889,8 +1921,12 @@
       </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
       <c r="AF8" s="1">
         <v>0</v>
       </c>
@@ -1917,8 +1953,12 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
       <c r="AF9" s="1">
         <v>0</v>
       </c>
@@ -1945,6 +1985,12 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AD10">
+        <v>16</v>
+      </c>
+      <c r="AE10">
+        <v>16</v>
+      </c>
       <c r="AF10">
         <v>16</v>
       </c>
@@ -1971,6 +2017,12 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AD11">
+        <v>16</v>
+      </c>
+      <c r="AE11">
+        <v>15</v>
+      </c>
       <c r="AF11">
         <v>10</v>
       </c>
@@ -1997,8 +2049,12 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
       <c r="AF12" s="1">
         <v>0</v>
       </c>
@@ -2025,6 +2081,12 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AD13">
+        <v>16</v>
+      </c>
+      <c r="AE13">
+        <v>16</v>
+      </c>
       <c r="AF13">
         <v>13</v>
       </c>
@@ -2053,8 +2115,12 @@
       </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>0</v>
+      </c>
       <c r="AF14" s="1">
         <v>0</v>
       </c>
@@ -2081,6 +2147,12 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AD15">
+        <v>16</v>
+      </c>
+      <c r="AE15">
+        <v>16</v>
+      </c>
       <c r="AF15">
         <v>17</v>
       </c>
@@ -2107,7 +2179,12 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="AE16" s="1"/>
+      <c r="AD16">
+        <v>16</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>0</v>
+      </c>
       <c r="AF16" s="1">
         <v>0</v>
       </c>
@@ -2134,6 +2211,12 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AD17">
+        <v>16</v>
+      </c>
+      <c r="AE17">
+        <v>16</v>
+      </c>
       <c r="AF17">
         <v>17</v>
       </c>
@@ -2162,8 +2245,12 @@
       </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>0</v>
+      </c>
       <c r="AF18" s="1">
         <v>0</v>
       </c>
@@ -2192,9 +2279,15 @@
       </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AF19" s="1"/>
+      <c r="AD19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="1">
+        <v>0</v>
+      </c>
       <c r="AG19" s="1">
         <v>0</v>
       </c>
@@ -2219,9 +2312,15 @@
         <v>18</v>
       </c>
       <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
+      <c r="AD20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="1">
+        <v>0</v>
+      </c>
       <c r="AG20" s="1">
         <v>0</v>
       </c>
@@ -2246,9 +2345,15 @@
         <v>19</v>
       </c>
       <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="1">
+        <v>0</v>
+      </c>
       <c r="AG21" s="1">
         <v>0</v>
       </c>
@@ -2272,6 +2377,12 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AD22">
+        <v>16</v>
+      </c>
+      <c r="AE22">
+        <v>16</v>
+      </c>
       <c r="AF22">
         <v>17</v>
       </c>
@@ -2298,6 +2409,12 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AD23">
+        <v>9</v>
+      </c>
+      <c r="AE23">
+        <v>15</v>
+      </c>
       <c r="AF23">
         <v>17</v>
       </c>
@@ -2326,8 +2443,12 @@
       </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
+      <c r="AD24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
       <c r="AF24" s="1">
         <v>0</v>
       </c>
@@ -2355,9 +2476,15 @@
         <v>44</v>
       </c>
       <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
+      <c r="AD25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="1">
+        <v>0</v>
+      </c>
       <c r="AG25" s="1">
         <v>0</v>
       </c>
@@ -2384,9 +2511,15 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
-      <c r="AF26" s="1"/>
+      <c r="AD26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="1">
+        <v>0</v>
+      </c>
       <c r="AG26" s="1">
         <v>0</v>
       </c>
@@ -2413,9 +2546,15 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
-      <c r="AF27" s="1"/>
+      <c r="AD27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="1">
+        <v>0</v>
+      </c>
       <c r="AG27" s="1">
         <v>0</v>
       </c>
@@ -2439,6 +2578,12 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AD28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>9</v>
+      </c>
       <c r="AF28">
         <v>17</v>
       </c>
@@ -2468,8 +2613,12 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
+      <c r="AD29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="1">
+        <v>0</v>
+      </c>
       <c r="AF29" s="1">
         <v>0</v>
       </c>
@@ -2499,8 +2648,12 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
+      <c r="AD30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1">
+        <v>0</v>
+      </c>
       <c r="AF30" s="1">
         <v>0</v>
       </c>
@@ -2528,8 +2681,12 @@
         <v>54</v>
       </c>
       <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
+      <c r="AD31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="1">
+        <v>0</v>
+      </c>
       <c r="AF31" s="1">
         <v>0</v>
       </c>
@@ -2559,8 +2716,12 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
+      <c r="AD32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>0</v>
+      </c>
       <c r="AF32" s="1">
         <v>0</v>
       </c>
@@ -2587,7 +2748,12 @@
       <c r="A33" t="s">
         <v>53</v>
       </c>
-      <c r="AE33" s="1"/>
+      <c r="AD33">
+        <v>16</v>
+      </c>
+      <c r="AE33" s="1">
+        <v>0</v>
+      </c>
       <c r="AF33" s="1">
         <v>0</v>
       </c>
@@ -2617,8 +2783,12 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
-      <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
+      <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>0</v>
+      </c>
       <c r="AF34" s="1">
         <v>0</v>
       </c>
@@ -2648,8 +2818,12 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
+      <c r="AD35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="1">
+        <v>0</v>
+      </c>
       <c r="AF35" s="1">
         <v>0</v>
       </c>
@@ -2679,8 +2853,12 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
-      <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
+      <c r="AD36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="1">
+        <v>0</v>
+      </c>
       <c r="AF36" s="1">
         <v>0</v>
       </c>
@@ -2710,8 +2888,12 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
-      <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
+      <c r="AD37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>0</v>
+      </c>
       <c r="AF37" s="1">
         <v>0</v>
       </c>
@@ -2741,8 +2923,12 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
+      <c r="AD38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>0</v>
+      </c>
       <c r="AF38" s="1">
         <v>0</v>
       </c>
@@ -2773,8 +2959,12 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
-      <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
+      <c r="AD39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="1">
+        <v>0</v>
+      </c>
       <c r="AF39" s="1">
         <v>0</v>
       </c>
@@ -2805,8 +2995,12 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
-      <c r="AD40" s="1"/>
-      <c r="AE40" s="1"/>
+      <c r="AD40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="1">
+        <v>0</v>
+      </c>
       <c r="AF40" s="1">
         <v>0</v>
       </c>
@@ -2833,7 +3027,12 @@
       <c r="A41" t="s">
         <v>64</v>
       </c>
-      <c r="AE41" s="1"/>
+      <c r="AD41">
+        <v>12</v>
+      </c>
+      <c r="AE41" s="1">
+        <v>0</v>
+      </c>
       <c r="AF41" s="1">
         <v>0</v>
       </c>
@@ -2864,8 +3063,12 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
-      <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="1">
+        <v>0</v>
+      </c>
       <c r="AF42" s="1">
         <v>0</v>
       </c>
@@ -2896,8 +3099,12 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
-      <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="1">
+        <v>0</v>
+      </c>
       <c r="AF43" s="1">
         <v>0</v>
       </c>
@@ -2929,8 +3136,12 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
+      <c r="AD44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="1">
+        <v>0</v>
+      </c>
       <c r="AF44" s="1">
         <v>0</v>
       </c>
@@ -2956,6 +3167,12 @@
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
+      </c>
+      <c r="AD45">
+        <v>16</v>
+      </c>
+      <c r="AE45">
+        <v>16</v>
       </c>
       <c r="AF45">
         <v>3</v>
@@ -2988,8 +3205,12 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
-      <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
+      <c r="AD46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="1">
+        <v>0</v>
+      </c>
       <c r="AF46" s="1">
         <v>0</v>
       </c>
@@ -3021,8 +3242,12 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
-      <c r="AD47" s="1"/>
-      <c r="AE47" s="1"/>
+      <c r="AD47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="1">
+        <v>0</v>
+      </c>
       <c r="AF47" s="1">
         <v>0</v>
       </c>
@@ -3054,8 +3279,12 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
-      <c r="AD48" s="1"/>
-      <c r="AE48" s="1"/>
+      <c r="AD48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1">
+        <v>0</v>
+      </c>
       <c r="AF48" s="1">
         <v>0</v>
       </c>
@@ -3087,8 +3316,12 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
-      <c r="AD49" s="1"/>
-      <c r="AE49" s="1"/>
+      <c r="AD49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="1">
+        <v>0</v>
+      </c>
       <c r="AF49" s="1">
         <v>0</v>
       </c>
@@ -3120,8 +3353,12 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
-      <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
+      <c r="AD50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="1">
+        <v>0</v>
+      </c>
       <c r="AF50" s="1">
         <v>0</v>
       </c>
@@ -3154,8 +3391,12 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
-      <c r="AD51" s="1"/>
-      <c r="AE51" s="1"/>
+      <c r="AD51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="1">
+        <v>0</v>
+      </c>
       <c r="AF51" s="1">
         <v>0</v>
       </c>
@@ -3188,8 +3429,12 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
-      <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
+      <c r="AD52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1">
+        <v>0</v>
+      </c>
       <c r="AF52" s="1">
         <v>0</v>
       </c>
@@ -3222,8 +3467,12 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
-      <c r="AD53" s="1"/>
-      <c r="AE53" s="1"/>
+      <c r="AD53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="1">
+        <v>0</v>
+      </c>
       <c r="AF53" s="1">
         <v>0</v>
       </c>
@@ -3256,8 +3505,12 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
-      <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
+      <c r="AD54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="1">
+        <v>0</v>
+      </c>
       <c r="AF54" s="1">
         <v>0</v>
       </c>
@@ -3290,8 +3543,12 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
-      <c r="AD55" s="1"/>
-      <c r="AE55" s="1"/>
+      <c r="AD55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="1">
+        <v>0</v>
+      </c>
       <c r="AF55" s="1">
         <v>0</v>
       </c>
@@ -3324,8 +3581,12 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
-      <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
+      <c r="AD56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="1">
+        <v>0</v>
+      </c>
       <c r="AF56" s="1">
         <v>0</v>
       </c>
@@ -3359,8 +3620,12 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
-      <c r="AD57" s="1"/>
-      <c r="AE57" s="1"/>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="1">
+        <v>0</v>
+      </c>
       <c r="AF57" s="1">
         <v>0</v>
       </c>
@@ -3394,8 +3659,12 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
-      <c r="AD58" s="1"/>
-      <c r="AE58" s="1"/>
+      <c r="AD58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="1">
+        <v>0</v>
+      </c>
       <c r="AF58" s="1">
         <v>0</v>
       </c>
@@ -3429,8 +3698,12 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
-      <c r="AD59" s="1"/>
-      <c r="AE59" s="1"/>
+      <c r="AD59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="1">
+        <v>0</v>
+      </c>
       <c r="AF59" s="1">
         <v>0</v>
       </c>
@@ -3464,8 +3737,12 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
-      <c r="AD60" s="1"/>
-      <c r="AE60" s="1"/>
+      <c r="AD60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="1">
+        <v>0</v>
+      </c>
       <c r="AF60" s="1">
         <v>0</v>
       </c>
@@ -3499,8 +3776,12 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
-      <c r="AD61" s="1"/>
-      <c r="AE61" s="1"/>
+      <c r="AD61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="1">
+        <v>0</v>
+      </c>
       <c r="AF61" s="1">
         <v>0</v>
       </c>
@@ -3535,8 +3816,12 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
-      <c r="AD62" s="1"/>
-      <c r="AE62" s="1"/>
+      <c r="AD62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="1">
+        <v>0</v>
+      </c>
       <c r="AF62" s="1">
         <v>0</v>
       </c>
@@ -3571,8 +3856,12 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
-      <c r="AD63" s="1"/>
-      <c r="AE63" s="1"/>
+      <c r="AD63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="1">
+        <v>0</v>
+      </c>
       <c r="AF63" s="1">
         <v>0</v>
       </c>
@@ -3608,8 +3897,12 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
-      <c r="AD64" s="1"/>
-      <c r="AE64" s="1"/>
+      <c r="AD64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="1">
+        <v>0</v>
+      </c>
       <c r="AF64" s="1">
         <v>0</v>
       </c>
@@ -3645,8 +3938,12 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
-      <c r="AD65" s="1"/>
-      <c r="AE65" s="1"/>
+      <c r="AD65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="1">
+        <v>0</v>
+      </c>
       <c r="AF65" s="1">
         <v>0</v>
       </c>
@@ -3682,8 +3979,12 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
-      <c r="AD66" s="1"/>
-      <c r="AE66" s="1"/>
+      <c r="AD66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="1">
+        <v>0</v>
+      </c>
       <c r="AF66" s="1">
         <v>0</v>
       </c>
@@ -3719,8 +4020,12 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
-      <c r="AD67" s="1"/>
-      <c r="AE67" s="1"/>
+      <c r="AD67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="1">
+        <v>0</v>
+      </c>
       <c r="AF67" s="1">
         <v>0</v>
       </c>
@@ -3747,7 +4052,12 @@
       <c r="A68" t="s">
         <v>92</v>
       </c>
-      <c r="AE68" s="1"/>
+      <c r="AD68">
+        <v>15</v>
+      </c>
+      <c r="AE68" s="1">
+        <v>0</v>
+      </c>
       <c r="AF68" s="1">
         <v>0</v>
       </c>
@@ -3784,8 +4094,12 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
-      <c r="AD69" s="1"/>
-      <c r="AE69" s="1"/>
+      <c r="AD69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="1">
+        <v>0</v>
+      </c>
       <c r="AF69" s="1">
         <v>0</v>
       </c>
@@ -3822,8 +4136,12 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
-      <c r="AD70" s="1"/>
-      <c r="AE70" s="1"/>
+      <c r="AD70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="1">
+        <v>0</v>
+      </c>
       <c r="AF70" s="1">
         <v>0</v>
       </c>
@@ -3860,8 +4178,12 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
-      <c r="AD71" s="1"/>
-      <c r="AE71" s="1"/>
+      <c r="AD71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="1">
+        <v>0</v>
+      </c>
       <c r="AF71" s="1">
         <v>0</v>
       </c>
@@ -3898,8 +4220,12 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
-      <c r="AD72" s="1"/>
-      <c r="AE72" s="1"/>
+      <c r="AD72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="1">
+        <v>0</v>
+      </c>
       <c r="AF72" s="1">
         <v>0</v>
       </c>
@@ -3936,8 +4262,12 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
-      <c r="AD73" s="1"/>
-      <c r="AE73" s="1"/>
+      <c r="AD73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="1">
+        <v>0</v>
+      </c>
       <c r="AF73" s="1">
         <v>0</v>
       </c>
@@ -3975,8 +4305,12 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
-      <c r="AD74" s="1"/>
-      <c r="AE74" s="1"/>
+      <c r="AD74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="1">
+        <v>0</v>
+      </c>
       <c r="AF74" s="1">
         <v>0</v>
       </c>
@@ -4014,8 +4348,12 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
-      <c r="AD75" s="1"/>
-      <c r="AE75" s="1"/>
+      <c r="AD75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="1">
+        <v>0</v>
+      </c>
       <c r="AF75" s="1">
         <v>0</v>
       </c>
@@ -4053,8 +4391,12 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
-      <c r="AD76" s="1"/>
-      <c r="AE76" s="1"/>
+      <c r="AD76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="1">
+        <v>0</v>
+      </c>
       <c r="AF76" s="1">
         <v>0</v>
       </c>
@@ -4092,8 +4434,12 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
-      <c r="AD77" s="1"/>
-      <c r="AE77" s="1"/>
+      <c r="AD77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="1">
+        <v>0</v>
+      </c>
       <c r="AF77" s="1">
         <v>0</v>
       </c>
@@ -4131,8 +4477,12 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
-      <c r="AD78" s="1"/>
-      <c r="AE78" s="1"/>
+      <c r="AD78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>0</v>
+      </c>
       <c r="AF78" s="1">
         <v>0</v>
       </c>
@@ -4171,8 +4521,12 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
-      <c r="AD79" s="1"/>
-      <c r="AE79" s="1"/>
+      <c r="AD79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="1">
+        <v>0</v>
+      </c>
       <c r="AF79" s="1">
         <v>0</v>
       </c>
@@ -4211,8 +4565,12 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
-      <c r="AD80" s="1"/>
-      <c r="AE80" s="1"/>
+      <c r="AD80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="1">
+        <v>0</v>
+      </c>
       <c r="AF80" s="1">
         <v>0</v>
       </c>
@@ -4252,8 +4610,12 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
-      <c r="AD81" s="1"/>
-      <c r="AE81" s="1"/>
+      <c r="AD81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="1">
+        <v>0</v>
+      </c>
       <c r="AF81" s="1">
         <v>0</v>
       </c>
@@ -4293,8 +4655,12 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
-      <c r="AD82" s="1"/>
-      <c r="AE82" s="1"/>
+      <c r="AD82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="1">
+        <v>0</v>
+      </c>
       <c r="AF82" s="1">
         <v>0</v>
       </c>
@@ -4334,8 +4700,12 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
-      <c r="AD83" s="1"/>
-      <c r="AE83" s="1"/>
+      <c r="AD83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="1">
+        <v>0</v>
+      </c>
       <c r="AF83" s="1">
         <v>0</v>
       </c>
@@ -4375,8 +4745,12 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
-      <c r="AD84" s="1"/>
-      <c r="AE84" s="1"/>
+      <c r="AD84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="1">
+        <v>0</v>
+      </c>
       <c r="AF84" s="1">
         <v>0</v>
       </c>
@@ -4416,8 +4790,12 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
-      <c r="AD85" s="1"/>
-      <c r="AE85" s="1"/>
+      <c r="AD85" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="1">
+        <v>0</v>
+      </c>
       <c r="AF85" s="1">
         <v>0</v>
       </c>
@@ -4458,8 +4836,12 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
-      <c r="AD86" s="1"/>
-      <c r="AE86" s="1"/>
+      <c r="AD86" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="1">
+        <v>0</v>
+      </c>
       <c r="AF86" s="1">
         <v>0</v>
       </c>
@@ -4500,8 +4882,12 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
-      <c r="AD87" s="1"/>
-      <c r="AE87" s="1"/>
+      <c r="AD87" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="1">
+        <v>0</v>
+      </c>
       <c r="AF87" s="1">
         <v>0</v>
       </c>
@@ -4542,8 +4928,12 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
-      <c r="AD88" s="1"/>
-      <c r="AE88" s="1"/>
+      <c r="AD88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="1">
+        <v>0</v>
+      </c>
       <c r="AF88" s="1">
         <v>0</v>
       </c>
@@ -4584,8 +4974,12 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
-      <c r="AD89" s="1"/>
-      <c r="AE89" s="1"/>
+      <c r="AD89" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="1">
+        <v>0</v>
+      </c>
       <c r="AF89" s="1">
         <v>0</v>
       </c>
@@ -4627,8 +5021,12 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
-      <c r="AD90" s="1"/>
-      <c r="AE90" s="1"/>
+      <c r="AD90" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="1">
+        <v>0</v>
+      </c>
       <c r="AF90" s="1">
         <v>0</v>
       </c>
@@ -4670,8 +5068,12 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
-      <c r="AD91" s="1"/>
-      <c r="AE91" s="1"/>
+      <c r="AD91" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="1">
+        <v>0</v>
+      </c>
       <c r="AF91" s="1">
         <v>0</v>
       </c>
@@ -4713,8 +5115,12 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
-      <c r="AD92" s="1"/>
-      <c r="AE92" s="1"/>
+      <c r="AD92" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="1">
+        <v>0</v>
+      </c>
       <c r="AF92" s="1">
         <v>0</v>
       </c>
@@ -4756,8 +5162,12 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
-      <c r="AD93" s="1"/>
-      <c r="AE93" s="1"/>
+      <c r="AD93" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="1">
+        <v>0</v>
+      </c>
       <c r="AF93" s="1">
         <v>0</v>
       </c>
@@ -4799,8 +5209,12 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
-      <c r="AD94" s="1"/>
-      <c r="AE94" s="1"/>
+      <c r="AD94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="1">
+        <v>0</v>
+      </c>
       <c r="AF94" s="1">
         <v>0</v>
       </c>
@@ -4843,8 +5257,12 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
-      <c r="AD95" s="1"/>
-      <c r="AE95" s="1"/>
+      <c r="AD95" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="1">
+        <v>0</v>
+      </c>
       <c r="AF95" s="1">
         <v>0</v>
       </c>
@@ -4887,8 +5305,12 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
-      <c r="AD96" s="1"/>
-      <c r="AE96" s="1"/>
+      <c r="AD96" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="1">
+        <v>0</v>
+      </c>
       <c r="AF96" s="1">
         <v>0</v>
       </c>
@@ -4931,8 +5353,12 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
-      <c r="AD97" s="1"/>
-      <c r="AE97" s="1"/>
+      <c r="AD97" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="1">
+        <v>0</v>
+      </c>
       <c r="AF97" s="1">
         <v>0</v>
       </c>
@@ -4975,8 +5401,12 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
-      <c r="AD98" s="1"/>
-      <c r="AE98" s="1"/>
+      <c r="AD98" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="1">
+        <v>0</v>
+      </c>
       <c r="AF98" s="1">
         <v>0</v>
       </c>
@@ -5019,8 +5449,12 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
-      <c r="AD99" s="1"/>
-      <c r="AE99" s="1"/>
+      <c r="AD99" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="1">
+        <v>0</v>
+      </c>
       <c r="AF99" s="1">
         <v>0</v>
       </c>
@@ -5064,8 +5498,12 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
-      <c r="AD100" s="1"/>
-      <c r="AE100" s="1"/>
+      <c r="AD100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="1">
+        <v>0</v>
+      </c>
       <c r="AF100" s="1">
         <v>0</v>
       </c>
@@ -5109,8 +5547,12 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
-      <c r="AD101" s="1"/>
-      <c r="AE101" s="1"/>
+      <c r="AD101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="1">
+        <v>0</v>
+      </c>
       <c r="AF101" s="1">
         <v>0</v>
       </c>
@@ -5154,8 +5596,12 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
-      <c r="AD102" s="1"/>
-      <c r="AE102" s="1"/>
+      <c r="AD102" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="1">
+        <v>0</v>
+      </c>
       <c r="AF102" s="1">
         <v>0</v>
       </c>
@@ -5199,8 +5645,12 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
-      <c r="AD103" s="1"/>
-      <c r="AE103" s="1"/>
+      <c r="AD103" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="1">
+        <v>0</v>
+      </c>
       <c r="AF103" s="1">
         <v>0</v>
       </c>
@@ -5245,8 +5695,12 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
-      <c r="AD104" s="1"/>
-      <c r="AE104" s="1"/>
+      <c r="AD104" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="1">
+        <v>0</v>
+      </c>
       <c r="AF104" s="1">
         <v>0</v>
       </c>
@@ -5291,8 +5745,12 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
-      <c r="AD105" s="1"/>
-      <c r="AE105" s="1"/>
+      <c r="AD105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="1">
+        <v>0</v>
+      </c>
       <c r="AF105" s="1">
         <v>0</v>
       </c>
@@ -5338,8 +5796,12 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
-      <c r="AD106" s="1"/>
-      <c r="AE106" s="1"/>
+      <c r="AD106" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="1">
+        <v>0</v>
+      </c>
       <c r="AF106" s="1">
         <v>0</v>
       </c>
@@ -5385,8 +5847,12 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
-      <c r="AD107" s="1"/>
-      <c r="AE107" s="1"/>
+      <c r="AD107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="1">
+        <v>0</v>
+      </c>
       <c r="AF107" s="1">
         <v>0</v>
       </c>
@@ -5432,8 +5898,12 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
-      <c r="AD108" s="1"/>
-      <c r="AE108" s="1"/>
+      <c r="AD108" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="1">
+        <v>0</v>
+      </c>
       <c r="AF108" s="1">
         <v>0</v>
       </c>
@@ -5480,8 +5950,12 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
-      <c r="AD109" s="1"/>
-      <c r="AE109" s="1"/>
+      <c r="AD109" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE109" s="1">
+        <v>0</v>
+      </c>
       <c r="AF109" s="1">
         <v>0</v>
       </c>
@@ -5528,8 +6002,12 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
-      <c r="AD110" s="1"/>
-      <c r="AE110" s="1"/>
+      <c r="AD110" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="1">
+        <v>0</v>
+      </c>
       <c r="AF110" s="1">
         <v>0</v>
       </c>
@@ -5576,8 +6054,12 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
-      <c r="AD111" s="1"/>
-      <c r="AE111" s="1"/>
+      <c r="AD111" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="1">
+        <v>0</v>
+      </c>
       <c r="AF111" s="1">
         <v>0</v>
       </c>
@@ -5625,8 +6107,12 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
-      <c r="AD112" s="1"/>
-      <c r="AE112" s="1"/>
+      <c r="AD112" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="1">
+        <v>0</v>
+      </c>
       <c r="AF112" s="1">
         <v>0</v>
       </c>
@@ -5674,8 +6160,12 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
-      <c r="AD113" s="1"/>
-      <c r="AE113" s="1"/>
+      <c r="AD113" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="1">
+        <v>0</v>
+      </c>
       <c r="AF113" s="1">
         <v>0</v>
       </c>
@@ -5723,8 +6213,12 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
-      <c r="AD114" s="1"/>
-      <c r="AE114" s="1"/>
+      <c r="AD114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="1">
+        <v>0</v>
+      </c>
       <c r="AF114" s="1">
         <v>0</v>
       </c>
@@ -5773,8 +6267,12 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
-      <c r="AD115" s="1"/>
-      <c r="AE115" s="1"/>
+      <c r="AD115" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE115" s="1">
+        <v>0</v>
+      </c>
       <c r="AF115" s="1">
         <v>0</v>
       </c>
@@ -5823,8 +6321,12 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
-      <c r="AD116" s="1"/>
-      <c r="AE116" s="1"/>
+      <c r="AD116" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="1">
+        <v>0</v>
+      </c>
       <c r="AF116" s="1">
         <v>0</v>
       </c>
@@ -5874,8 +6376,12 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
-      <c r="AD117" s="1"/>
-      <c r="AE117" s="1"/>
+      <c r="AD117" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE117" s="1">
+        <v>0</v>
+      </c>
       <c r="AF117" s="1">
         <v>0</v>
       </c>
@@ -5925,8 +6431,12 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
-      <c r="AD118" s="1"/>
-      <c r="AE118" s="1"/>
+      <c r="AD118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="1">
+        <v>0</v>
+      </c>
       <c r="AF118" s="1">
         <v>0</v>
       </c>
@@ -5976,8 +6486,12 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
-      <c r="AD119" s="1"/>
-      <c r="AE119" s="1"/>
+      <c r="AD119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="1">
+        <v>0</v>
+      </c>
       <c r="AF119" s="1">
         <v>0</v>
       </c>
@@ -6028,8 +6542,12 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
-      <c r="AD120" s="1"/>
-      <c r="AE120" s="1"/>
+      <c r="AD120" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE120" s="1">
+        <v>0</v>
+      </c>
       <c r="AF120" s="1">
         <v>0</v>
       </c>
@@ -6080,8 +6598,12 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
-      <c r="AD121" s="1"/>
-      <c r="AE121" s="1"/>
+      <c r="AD121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE121" s="1">
+        <v>0</v>
+      </c>
       <c r="AF121" s="1">
         <v>0</v>
       </c>
@@ -6132,8 +6654,12 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
-      <c r="AD122" s="1"/>
-      <c r="AE122" s="1"/>
+      <c r="AD122" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE122" s="1">
+        <v>0</v>
+      </c>
       <c r="AF122" s="1">
         <v>0</v>
       </c>
@@ -6185,8 +6711,12 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
-      <c r="AD123" s="1"/>
-      <c r="AE123" s="1"/>
+      <c r="AD123" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE123" s="1">
+        <v>0</v>
+      </c>
       <c r="AF123" s="1">
         <v>0</v>
       </c>
@@ -6238,8 +6768,12 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
-      <c r="AD124" s="1"/>
-      <c r="AE124" s="1"/>
+      <c r="AD124" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE124" s="1">
+        <v>0</v>
+      </c>
       <c r="AF124" s="1">
         <v>0</v>
       </c>
@@ -6291,8 +6825,12 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
-      <c r="AD125" s="1"/>
-      <c r="AE125" s="1"/>
+      <c r="AD125" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE125" s="1">
+        <v>0</v>
+      </c>
       <c r="AF125" s="1">
         <v>0</v>
       </c>
@@ -6345,8 +6883,12 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
-      <c r="AD126" s="1"/>
-      <c r="AE126" s="1"/>
+      <c r="AD126" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE126" s="1">
+        <v>0</v>
+      </c>
       <c r="AF126" s="1">
         <v>0</v>
       </c>
@@ -6377,12 +6919,995 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B17" si="0">SUM(C3:R3)</f>
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCF17F8-9A94-4DD9-8AD7-5B5DF04802D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21409134-6BD0-4CA6-8AA5-0F5A7316DD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1725,6 +1725,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AC2">
+        <v>17</v>
+      </c>
       <c r="AD2">
         <v>9</v>
       </c>
@@ -1750,13 +1753,16 @@
         <v>16</v>
       </c>
       <c r="AL2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AC3">
+        <v>17</v>
+      </c>
       <c r="AD3">
         <v>16</v>
       </c>
@@ -1789,7 +1795,9 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="AC4" s="1"/>
+      <c r="AC4" s="1">
+        <v>0</v>
+      </c>
       <c r="AD4" s="1">
         <v>0</v>
       </c>
@@ -1822,6 +1830,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AC5">
+        <v>17</v>
+      </c>
       <c r="AD5">
         <v>16</v>
       </c>
@@ -1854,7 +1865,9 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="AC6" s="1"/>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
       <c r="AD6" s="1">
         <v>0</v>
       </c>
@@ -1887,6 +1900,9 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AC7">
+        <v>17</v>
+      </c>
       <c r="AD7">
         <v>16</v>
       </c>
@@ -1920,7 +1936,9 @@
         <v>7</v>
       </c>
       <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
+      <c r="AC8" s="1">
+        <v>0</v>
+      </c>
       <c r="AD8" s="1">
         <v>0</v>
       </c>
@@ -1953,6 +1971,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AC9">
+        <v>16</v>
+      </c>
       <c r="AD9" s="1">
         <v>0</v>
       </c>
@@ -1985,6 +2006,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AC10">
+        <v>17</v>
+      </c>
       <c r="AD10">
         <v>16</v>
       </c>
@@ -2017,6 +2041,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AC11" s="1">
+        <v>0</v>
+      </c>
       <c r="AD11">
         <v>16</v>
       </c>
@@ -2049,6 +2076,9 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="AC12">
+        <v>17</v>
+      </c>
       <c r="AD12" s="1">
         <v>0</v>
       </c>
@@ -2081,6 +2111,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AC13">
+        <v>17</v>
+      </c>
       <c r="AD13">
         <v>16</v>
       </c>
@@ -2114,7 +2147,9 @@
         <v>13</v>
       </c>
       <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
       <c r="AD14" s="1">
         <v>0</v>
       </c>
@@ -2147,6 +2182,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AC15">
+        <v>17</v>
+      </c>
       <c r="AD15">
         <v>16</v>
       </c>
@@ -2179,6 +2217,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AC16">
+        <v>16</v>
+      </c>
       <c r="AD16">
         <v>16</v>
       </c>
@@ -2211,6 +2252,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AC17">
+        <v>16</v>
+      </c>
       <c r="AD17">
         <v>16</v>
       </c>
@@ -2244,7 +2288,9 @@
         <v>17</v>
       </c>
       <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
+      <c r="AC18" s="1">
+        <v>0</v>
+      </c>
       <c r="AD18" s="1">
         <v>0</v>
       </c>
@@ -2278,7 +2324,9 @@
         <v>85</v>
       </c>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
+      <c r="AC19" s="1">
+        <v>0</v>
+      </c>
       <c r="AD19" s="1">
         <v>0</v>
       </c>
@@ -2311,7 +2359,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="AC20" s="1"/>
+      <c r="AC20" s="1">
+        <v>0</v>
+      </c>
       <c r="AD20" s="1">
         <v>0</v>
       </c>
@@ -2344,7 +2394,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="AC21" s="1"/>
+      <c r="AC21" s="1">
+        <v>0</v>
+      </c>
       <c r="AD21" s="1">
         <v>0</v>
       </c>
@@ -2377,6 +2429,9 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AC22">
+        <v>17</v>
+      </c>
       <c r="AD22">
         <v>16</v>
       </c>
@@ -2409,6 +2464,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AC23">
+        <v>15</v>
+      </c>
       <c r="AD23">
         <v>9</v>
       </c>
@@ -2442,7 +2500,9 @@
         <v>22</v>
       </c>
       <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
+      <c r="AC24" s="1">
+        <v>0</v>
+      </c>
       <c r="AD24" s="1">
         <v>0</v>
       </c>
@@ -2475,7 +2535,9 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
-      <c r="AC25" s="1"/>
+      <c r="AC25" s="1">
+        <v>0</v>
+      </c>
       <c r="AD25" s="1">
         <v>0</v>
       </c>
@@ -2510,7 +2572,9 @@
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
+      <c r="AC26" s="1">
+        <v>0</v>
+      </c>
       <c r="AD26" s="1">
         <v>0</v>
       </c>
@@ -2545,7 +2609,9 @@
       </c>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
+      <c r="AC27" s="1">
+        <v>0</v>
+      </c>
       <c r="AD27" s="1">
         <v>0</v>
       </c>
@@ -2578,6 +2644,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AC28">
+        <v>17</v>
+      </c>
       <c r="AD28" s="1">
         <v>0</v>
       </c>
@@ -2612,7 +2681,9 @@
       </c>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
+      <c r="AC29" s="1">
+        <v>0</v>
+      </c>
       <c r="AD29" s="1">
         <v>0</v>
       </c>
@@ -2647,7 +2718,9 @@
       </c>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
+      <c r="AC30" s="1">
+        <v>0</v>
+      </c>
       <c r="AD30" s="1">
         <v>0</v>
       </c>
@@ -2680,7 +2753,9 @@
       <c r="A31" t="s">
         <v>54</v>
       </c>
-      <c r="AC31" s="1"/>
+      <c r="AC31" s="1">
+        <v>0</v>
+      </c>
       <c r="AD31" s="1">
         <v>0</v>
       </c>
@@ -2715,7 +2790,9 @@
       </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
+      <c r="AC32" s="1">
+        <v>0</v>
+      </c>
       <c r="AD32" s="1">
         <v>0</v>
       </c>
@@ -2748,6 +2825,9 @@
       <c r="A33" t="s">
         <v>53</v>
       </c>
+      <c r="AC33">
+        <v>17</v>
+      </c>
       <c r="AD33">
         <v>16</v>
       </c>
@@ -2782,7 +2862,9 @@
       </c>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
+      <c r="AC34" s="1">
+        <v>0</v>
+      </c>
       <c r="AD34" s="1">
         <v>0</v>
       </c>
@@ -2817,7 +2899,9 @@
       </c>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
+      <c r="AC35" s="1">
+        <v>0</v>
+      </c>
       <c r="AD35" s="1">
         <v>0</v>
       </c>
@@ -2852,7 +2936,9 @@
       </c>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
+      <c r="AC36" s="1">
+        <v>0</v>
+      </c>
       <c r="AD36" s="1">
         <v>0</v>
       </c>
@@ -2887,7 +2973,9 @@
       </c>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
+      <c r="AC37" s="1">
+        <v>0</v>
+      </c>
       <c r="AD37" s="1">
         <v>0</v>
       </c>
@@ -2922,7 +3010,9 @@
       </c>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
+      <c r="AC38" s="1">
+        <v>0</v>
+      </c>
       <c r="AD38" s="1">
         <v>0</v>
       </c>
@@ -2958,7 +3048,9 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
+      <c r="AC39" s="1">
+        <v>0</v>
+      </c>
       <c r="AD39" s="1">
         <v>0</v>
       </c>
@@ -2994,7 +3086,9 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
+      <c r="AC40" s="1">
+        <v>0</v>
+      </c>
       <c r="AD40" s="1">
         <v>0</v>
       </c>
@@ -3027,6 +3121,9 @@
       <c r="A41" t="s">
         <v>64</v>
       </c>
+      <c r="AC41">
+        <v>17</v>
+      </c>
       <c r="AD41">
         <v>12</v>
       </c>
@@ -3062,7 +3159,9 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
+      <c r="AC42" s="1">
+        <v>0</v>
+      </c>
       <c r="AD42" s="1">
         <v>0</v>
       </c>
@@ -3098,7 +3197,9 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
+      <c r="AC43" s="1">
+        <v>0</v>
+      </c>
       <c r="AD43" s="1">
         <v>0</v>
       </c>
@@ -3135,7 +3236,9 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
+      <c r="AC44" s="1">
+        <v>0</v>
+      </c>
       <c r="AD44" s="1">
         <v>0</v>
       </c>
@@ -3167,6 +3270,9 @@
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
+      </c>
+      <c r="AC45">
+        <v>17</v>
       </c>
       <c r="AD45">
         <v>16</v>
@@ -3204,7 +3310,9 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
+      <c r="AC46" s="1">
+        <v>0</v>
+      </c>
       <c r="AD46" s="1">
         <v>0</v>
       </c>
@@ -3241,7 +3349,9 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
-      <c r="AC47" s="1"/>
+      <c r="AC47" s="1">
+        <v>0</v>
+      </c>
       <c r="AD47" s="1">
         <v>0</v>
       </c>
@@ -3278,7 +3388,9 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
-      <c r="AC48" s="1"/>
+      <c r="AC48" s="1">
+        <v>0</v>
+      </c>
       <c r="AD48" s="1">
         <v>0</v>
       </c>
@@ -3315,7 +3427,9 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
-      <c r="AC49" s="1"/>
+      <c r="AC49" s="1">
+        <v>0</v>
+      </c>
       <c r="AD49" s="1">
         <v>0</v>
       </c>
@@ -3352,7 +3466,9 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
-      <c r="AC50" s="1"/>
+      <c r="AC50" s="1">
+        <v>0</v>
+      </c>
       <c r="AD50" s="1">
         <v>0</v>
       </c>
@@ -3390,7 +3506,9 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
-      <c r="AC51" s="1"/>
+      <c r="AC51" s="1">
+        <v>0</v>
+      </c>
       <c r="AD51" s="1">
         <v>0</v>
       </c>
@@ -3428,7 +3546,9 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
-      <c r="AC52" s="1"/>
+      <c r="AC52" s="1">
+        <v>0</v>
+      </c>
       <c r="AD52" s="1">
         <v>0</v>
       </c>
@@ -3466,7 +3586,9 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
-      <c r="AC53" s="1"/>
+      <c r="AC53" s="1">
+        <v>0</v>
+      </c>
       <c r="AD53" s="1">
         <v>0</v>
       </c>
@@ -3504,7 +3626,9 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
+      <c r="AC54" s="1">
+        <v>0</v>
+      </c>
       <c r="AD54" s="1">
         <v>0</v>
       </c>
@@ -3542,7 +3666,9 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
-      <c r="AC55" s="1"/>
+      <c r="AC55" s="1">
+        <v>0</v>
+      </c>
       <c r="AD55" s="1">
         <v>0</v>
       </c>
@@ -3580,7 +3706,9 @@
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
-      <c r="AC56" s="1"/>
+      <c r="AC56" s="1">
+        <v>0</v>
+      </c>
       <c r="AD56" s="1">
         <v>0</v>
       </c>
@@ -3619,7 +3747,9 @@
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
-      <c r="AC57" s="1"/>
+      <c r="AC57" s="1">
+        <v>0</v>
+      </c>
       <c r="AD57" s="1">
         <v>0</v>
       </c>
@@ -3658,7 +3788,9 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
-      <c r="AC58" s="1"/>
+      <c r="AC58" s="1">
+        <v>0</v>
+      </c>
       <c r="AD58" s="1">
         <v>0</v>
       </c>
@@ -3697,7 +3829,9 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
-      <c r="AC59" s="1"/>
+      <c r="AC59" s="1">
+        <v>0</v>
+      </c>
       <c r="AD59" s="1">
         <v>0</v>
       </c>
@@ -3736,7 +3870,9 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
-      <c r="AC60" s="1"/>
+      <c r="AC60" s="1">
+        <v>0</v>
+      </c>
       <c r="AD60" s="1">
         <v>0</v>
       </c>
@@ -3775,7 +3911,9 @@
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
-      <c r="AC61" s="1"/>
+      <c r="AC61" s="1">
+        <v>0</v>
+      </c>
       <c r="AD61" s="1">
         <v>0</v>
       </c>
@@ -3815,7 +3953,9 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
-      <c r="AC62" s="1"/>
+      <c r="AC62" s="1">
+        <v>0</v>
+      </c>
       <c r="AD62" s="1">
         <v>0</v>
       </c>
@@ -3855,7 +3995,9 @@
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
-      <c r="AC63" s="1"/>
+      <c r="AC63" s="1">
+        <v>0</v>
+      </c>
       <c r="AD63" s="1">
         <v>0</v>
       </c>
@@ -3896,7 +4038,9 @@
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
-      <c r="AC64" s="1"/>
+      <c r="AC64" s="1">
+        <v>0</v>
+      </c>
       <c r="AD64" s="1">
         <v>0</v>
       </c>
@@ -3937,7 +4081,9 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
-      <c r="AC65" s="1"/>
+      <c r="AC65" s="1">
+        <v>0</v>
+      </c>
       <c r="AD65" s="1">
         <v>0</v>
       </c>
@@ -3978,7 +4124,9 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
-      <c r="AC66" s="1"/>
+      <c r="AC66" s="1">
+        <v>0</v>
+      </c>
       <c r="AD66" s="1">
         <v>0</v>
       </c>
@@ -4019,7 +4167,9 @@
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
-      <c r="AC67" s="1"/>
+      <c r="AC67" s="1">
+        <v>0</v>
+      </c>
       <c r="AD67" s="1">
         <v>0</v>
       </c>
@@ -4051,6 +4201,33 @@
     <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>92</v>
+      </c>
+      <c r="U68" s="1">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="1">
+        <v>0</v>
       </c>
       <c r="AD68">
         <v>15</v>
@@ -4093,7 +4270,9 @@
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
-      <c r="AC69" s="1"/>
+      <c r="AC69" s="1">
+        <v>0</v>
+      </c>
       <c r="AD69" s="1">
         <v>0</v>
       </c>
@@ -4135,7 +4314,9 @@
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
-      <c r="AC70" s="1"/>
+      <c r="AC70" s="1">
+        <v>0</v>
+      </c>
       <c r="AD70" s="1">
         <v>0</v>
       </c>
@@ -4177,7 +4358,9 @@
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
-      <c r="AC71" s="1"/>
+      <c r="AC71" s="1">
+        <v>0</v>
+      </c>
       <c r="AD71" s="1">
         <v>0</v>
       </c>
@@ -4219,7 +4402,9 @@
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
-      <c r="AC72" s="1"/>
+      <c r="AC72" s="1">
+        <v>0</v>
+      </c>
       <c r="AD72" s="1">
         <v>0</v>
       </c>
@@ -4261,7 +4446,9 @@
       <c r="Z73" s="1"/>
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
-      <c r="AC73" s="1"/>
+      <c r="AC73" s="1">
+        <v>0</v>
+      </c>
       <c r="AD73" s="1">
         <v>0</v>
       </c>
@@ -4304,7 +4491,9 @@
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
-      <c r="AC74" s="1"/>
+      <c r="AC74" s="1">
+        <v>0</v>
+      </c>
       <c r="AD74" s="1">
         <v>0</v>
       </c>
@@ -4347,7 +4536,9 @@
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
-      <c r="AC75" s="1"/>
+      <c r="AC75" s="1">
+        <v>0</v>
+      </c>
       <c r="AD75" s="1">
         <v>0</v>
       </c>
@@ -4390,7 +4581,9 @@
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
-      <c r="AC76" s="1"/>
+      <c r="AC76" s="1">
+        <v>0</v>
+      </c>
       <c r="AD76" s="1">
         <v>0</v>
       </c>
@@ -4433,7 +4626,9 @@
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
-      <c r="AC77" s="1"/>
+      <c r="AC77" s="1">
+        <v>0</v>
+      </c>
       <c r="AD77" s="1">
         <v>0</v>
       </c>
@@ -4476,7 +4671,9 @@
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
-      <c r="AC78" s="1"/>
+      <c r="AC78" s="1">
+        <v>0</v>
+      </c>
       <c r="AD78" s="1">
         <v>0</v>
       </c>
@@ -4520,7 +4717,9 @@
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
-      <c r="AC79" s="1"/>
+      <c r="AC79" s="1">
+        <v>0</v>
+      </c>
       <c r="AD79" s="1">
         <v>0</v>
       </c>
@@ -4564,7 +4763,9 @@
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
-      <c r="AC80" s="1"/>
+      <c r="AC80" s="1">
+        <v>0</v>
+      </c>
       <c r="AD80" s="1">
         <v>0</v>
       </c>
@@ -4609,7 +4810,9 @@
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
-      <c r="AC81" s="1"/>
+      <c r="AC81" s="1">
+        <v>0</v>
+      </c>
       <c r="AD81" s="1">
         <v>0</v>
       </c>
@@ -4654,7 +4857,9 @@
       <c r="Z82" s="1"/>
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
-      <c r="AC82" s="1"/>
+      <c r="AC82" s="1">
+        <v>0</v>
+      </c>
       <c r="AD82" s="1">
         <v>0</v>
       </c>
@@ -4699,7 +4904,9 @@
       <c r="Z83" s="1"/>
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
-      <c r="AC83" s="1"/>
+      <c r="AC83" s="1">
+        <v>0</v>
+      </c>
       <c r="AD83" s="1">
         <v>0</v>
       </c>
@@ -4744,7 +4951,9 @@
       <c r="Z84" s="1"/>
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
-      <c r="AC84" s="1"/>
+      <c r="AC84" s="1">
+        <v>0</v>
+      </c>
       <c r="AD84" s="1">
         <v>0</v>
       </c>
@@ -4789,7 +4998,9 @@
       <c r="Z85" s="1"/>
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
-      <c r="AC85" s="1"/>
+      <c r="AC85" s="1">
+        <v>0</v>
+      </c>
       <c r="AD85" s="1">
         <v>0</v>
       </c>
@@ -4835,7 +5046,9 @@
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
-      <c r="AC86" s="1"/>
+      <c r="AC86" s="1">
+        <v>0</v>
+      </c>
       <c r="AD86" s="1">
         <v>0</v>
       </c>
@@ -4881,7 +5094,9 @@
       <c r="Z87" s="1"/>
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
-      <c r="AC87" s="1"/>
+      <c r="AC87" s="1">
+        <v>0</v>
+      </c>
       <c r="AD87" s="1">
         <v>0</v>
       </c>
@@ -4927,7 +5142,9 @@
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
-      <c r="AC88" s="1"/>
+      <c r="AC88" s="1">
+        <v>0</v>
+      </c>
       <c r="AD88" s="1">
         <v>0</v>
       </c>
@@ -4973,7 +5190,9 @@
       <c r="Z89" s="1"/>
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
-      <c r="AC89" s="1"/>
+      <c r="AC89" s="1">
+        <v>0</v>
+      </c>
       <c r="AD89" s="1">
         <v>0</v>
       </c>
@@ -5020,7 +5239,9 @@
       <c r="Z90" s="1"/>
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
-      <c r="AC90" s="1"/>
+      <c r="AC90" s="1">
+        <v>0</v>
+      </c>
       <c r="AD90" s="1">
         <v>0</v>
       </c>
@@ -5067,7 +5288,9 @@
       <c r="Z91" s="1"/>
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
-      <c r="AC91" s="1"/>
+      <c r="AC91" s="1">
+        <v>0</v>
+      </c>
       <c r="AD91" s="1">
         <v>0</v>
       </c>
@@ -5114,7 +5337,9 @@
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
-      <c r="AC92" s="1"/>
+      <c r="AC92" s="1">
+        <v>0</v>
+      </c>
       <c r="AD92" s="1">
         <v>0</v>
       </c>
@@ -5161,7 +5386,9 @@
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
-      <c r="AC93" s="1"/>
+      <c r="AC93" s="1">
+        <v>0</v>
+      </c>
       <c r="AD93" s="1">
         <v>0</v>
       </c>
@@ -5208,7 +5435,9 @@
       <c r="Z94" s="1"/>
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
-      <c r="AC94" s="1"/>
+      <c r="AC94" s="1">
+        <v>0</v>
+      </c>
       <c r="AD94" s="1">
         <v>0</v>
       </c>
@@ -5256,7 +5485,9 @@
       <c r="Z95" s="1"/>
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
-      <c r="AC95" s="1"/>
+      <c r="AC95" s="1">
+        <v>0</v>
+      </c>
       <c r="AD95" s="1">
         <v>0</v>
       </c>
@@ -5304,7 +5535,9 @@
       <c r="Z96" s="1"/>
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
-      <c r="AC96" s="1"/>
+      <c r="AC96" s="1">
+        <v>0</v>
+      </c>
       <c r="AD96" s="1">
         <v>0</v>
       </c>
@@ -5352,7 +5585,9 @@
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
-      <c r="AC97" s="1"/>
+      <c r="AC97" s="1">
+        <v>0</v>
+      </c>
       <c r="AD97" s="1">
         <v>0</v>
       </c>
@@ -5400,7 +5635,9 @@
       <c r="Z98" s="1"/>
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
-      <c r="AC98" s="1"/>
+      <c r="AC98" s="1">
+        <v>0</v>
+      </c>
       <c r="AD98" s="1">
         <v>0</v>
       </c>
@@ -5448,7 +5685,9 @@
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
-      <c r="AC99" s="1"/>
+      <c r="AC99" s="1">
+        <v>0</v>
+      </c>
       <c r="AD99" s="1">
         <v>0</v>
       </c>
@@ -5497,7 +5736,9 @@
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
-      <c r="AC100" s="1"/>
+      <c r="AC100" s="1">
+        <v>0</v>
+      </c>
       <c r="AD100" s="1">
         <v>0</v>
       </c>
@@ -5546,7 +5787,9 @@
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
-      <c r="AC101" s="1"/>
+      <c r="AC101" s="1">
+        <v>0</v>
+      </c>
       <c r="AD101" s="1">
         <v>0</v>
       </c>
@@ -5595,7 +5838,9 @@
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
-      <c r="AC102" s="1"/>
+      <c r="AC102" s="1">
+        <v>0</v>
+      </c>
       <c r="AD102" s="1">
         <v>0</v>
       </c>
@@ -5644,7 +5889,9 @@
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
-      <c r="AC103" s="1"/>
+      <c r="AC103" s="1">
+        <v>0</v>
+      </c>
       <c r="AD103" s="1">
         <v>0</v>
       </c>
@@ -5694,7 +5941,9 @@
       <c r="Z104" s="1"/>
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
-      <c r="AC104" s="1"/>
+      <c r="AC104" s="1">
+        <v>0</v>
+      </c>
       <c r="AD104" s="1">
         <v>0</v>
       </c>
@@ -5744,7 +5993,9 @@
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
-      <c r="AC105" s="1"/>
+      <c r="AC105" s="1">
+        <v>0</v>
+      </c>
       <c r="AD105" s="1">
         <v>0</v>
       </c>
@@ -5795,7 +6046,9 @@
       <c r="Z106" s="1"/>
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
-      <c r="AC106" s="1"/>
+      <c r="AC106" s="1">
+        <v>0</v>
+      </c>
       <c r="AD106" s="1">
         <v>0</v>
       </c>
@@ -5846,7 +6099,9 @@
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
-      <c r="AC107" s="1"/>
+      <c r="AC107" s="1">
+        <v>0</v>
+      </c>
       <c r="AD107" s="1">
         <v>0</v>
       </c>
@@ -5897,7 +6152,9 @@
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
-      <c r="AC108" s="1"/>
+      <c r="AC108" s="1">
+        <v>0</v>
+      </c>
       <c r="AD108" s="1">
         <v>0</v>
       </c>
@@ -5949,7 +6206,9 @@
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
-      <c r="AC109" s="1"/>
+      <c r="AC109" s="1">
+        <v>0</v>
+      </c>
       <c r="AD109" s="1">
         <v>0</v>
       </c>
@@ -6001,7 +6260,9 @@
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
-      <c r="AC110" s="1"/>
+      <c r="AC110" s="1">
+        <v>0</v>
+      </c>
       <c r="AD110" s="1">
         <v>0</v>
       </c>
@@ -6053,7 +6314,9 @@
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
-      <c r="AC111" s="1"/>
+      <c r="AC111" s="1">
+        <v>0</v>
+      </c>
       <c r="AD111" s="1">
         <v>0</v>
       </c>
@@ -6106,7 +6369,9 @@
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
-      <c r="AC112" s="1"/>
+      <c r="AC112" s="1">
+        <v>0</v>
+      </c>
       <c r="AD112" s="1">
         <v>0</v>
       </c>
@@ -6159,7 +6424,9 @@
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
-      <c r="AC113" s="1"/>
+      <c r="AC113" s="1">
+        <v>0</v>
+      </c>
       <c r="AD113" s="1">
         <v>0</v>
       </c>
@@ -6212,7 +6479,9 @@
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
-      <c r="AC114" s="1"/>
+      <c r="AC114" s="1">
+        <v>0</v>
+      </c>
       <c r="AD114" s="1">
         <v>0</v>
       </c>
@@ -6266,7 +6535,9 @@
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
-      <c r="AC115" s="1"/>
+      <c r="AC115" s="1">
+        <v>0</v>
+      </c>
       <c r="AD115" s="1">
         <v>0</v>
       </c>
@@ -6320,7 +6591,9 @@
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
-      <c r="AC116" s="1"/>
+      <c r="AC116" s="1">
+        <v>0</v>
+      </c>
       <c r="AD116" s="1">
         <v>0</v>
       </c>
@@ -6375,7 +6648,9 @@
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
-      <c r="AC117" s="1"/>
+      <c r="AC117" s="1">
+        <v>0</v>
+      </c>
       <c r="AD117" s="1">
         <v>0</v>
       </c>
@@ -6430,7 +6705,9 @@
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
-      <c r="AC118" s="1"/>
+      <c r="AC118" s="1">
+        <v>0</v>
+      </c>
       <c r="AD118" s="1">
         <v>0</v>
       </c>
@@ -6485,7 +6762,9 @@
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
-      <c r="AC119" s="1"/>
+      <c r="AC119" s="1">
+        <v>0</v>
+      </c>
       <c r="AD119" s="1">
         <v>0</v>
       </c>
@@ -6541,7 +6820,9 @@
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
-      <c r="AC120" s="1"/>
+      <c r="AC120" s="1">
+        <v>0</v>
+      </c>
       <c r="AD120" s="1">
         <v>0</v>
       </c>
@@ -6597,7 +6878,9 @@
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
-      <c r="AC121" s="1"/>
+      <c r="AC121" s="1">
+        <v>0</v>
+      </c>
       <c r="AD121" s="1">
         <v>0</v>
       </c>
@@ -6653,7 +6936,9 @@
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
-      <c r="AC122" s="1"/>
+      <c r="AC122" s="1">
+        <v>0</v>
+      </c>
       <c r="AD122" s="1">
         <v>0</v>
       </c>
@@ -6710,7 +6995,9 @@
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
-      <c r="AC123" s="1"/>
+      <c r="AC123" s="1">
+        <v>0</v>
+      </c>
       <c r="AD123" s="1">
         <v>0</v>
       </c>
@@ -6767,7 +7054,9 @@
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
-      <c r="AC124" s="1"/>
+      <c r="AC124" s="1">
+        <v>0</v>
+      </c>
       <c r="AD124" s="1">
         <v>0</v>
       </c>
@@ -6824,7 +7113,9 @@
       <c r="Z125" s="1"/>
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
-      <c r="AC125" s="1"/>
+      <c r="AC125" s="1">
+        <v>0</v>
+      </c>
       <c r="AD125" s="1">
         <v>0</v>
       </c>
@@ -6882,7 +7173,9 @@
       <c r="Z126" s="1"/>
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
-      <c r="AC126" s="1"/>
+      <c r="AC126" s="1">
+        <v>0</v>
+      </c>
       <c r="AD126" s="1">
         <v>0</v>
       </c>
@@ -7914,12 +8207,1107 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC06B72-571E-40C4-AD69-3294909EA05A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:S2)</f>
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B18" si="0">SUM(C3:S3)</f>
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9153,7 +10541,7 @@
       </c>
       <c r="B2">
         <f>SUM(C2:R2)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -9186,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
         <v>1</v>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21409134-6BD0-4CA6-8AA5-0F5A7316DD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6784A2D-06EB-446A-860B-507FC7810C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="4" activeTab="11" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1084,13 +1084,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1133,13 +1133,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1601,7 +1601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AL126"/>
+  <dimension ref="A1:AL124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -2751,13 +2751,13 @@
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="AC31">
+        <v>17</v>
+      </c>
+      <c r="AD31">
+        <v>16</v>
       </c>
       <c r="AE31" s="1">
         <v>0</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
@@ -2823,13 +2823,15 @@
     </row>
     <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC33">
-        <v>17</v>
-      </c>
-      <c r="AD33">
-        <v>16</v>
+        <v>58</v>
+      </c>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="1">
+        <v>0</v>
       </c>
       <c r="AE33" s="1">
         <v>0</v>
@@ -2858,7 +2860,7 @@
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
@@ -2895,7 +2897,7 @@
     </row>
     <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
@@ -2932,7 +2934,7 @@
     </row>
     <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
@@ -2969,8 +2971,9 @@
     </row>
     <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>60</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1">
@@ -3006,8 +3009,9 @@
     </row>
     <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>61</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1">
@@ -3043,16 +3047,13 @@
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="1">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="AC39">
+        <v>17</v>
+      </c>
+      <c r="AD39">
+        <v>12</v>
       </c>
       <c r="AE39" s="1">
         <v>0</v>
@@ -3081,7 +3082,7 @@
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
@@ -3119,13 +3120,16 @@
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC41">
-        <v>17</v>
-      </c>
-      <c r="AD41">
-        <v>12</v>
+        <v>66</v>
+      </c>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>0</v>
       </c>
       <c r="AE41" s="1">
         <v>0</v>
@@ -3154,8 +3158,9 @@
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>65</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
@@ -3192,22 +3197,19 @@
     </row>
     <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="AC43">
+        <v>17</v>
+      </c>
+      <c r="AD43">
+        <v>16</v>
+      </c>
+      <c r="AE43">
+        <v>16</v>
+      </c>
+      <c r="AF43">
+        <v>3</v>
       </c>
       <c r="AG43" s="1">
         <v>0</v>
@@ -3230,7 +3232,7 @@
     </row>
     <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -3269,19 +3271,23 @@
     </row>
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC45">
-        <v>17</v>
-      </c>
-      <c r="AD45">
-        <v>16</v>
-      </c>
-      <c r="AE45">
-        <v>16</v>
-      </c>
-      <c r="AF45">
-        <v>3</v>
+        <v>70</v>
+      </c>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="1">
+        <v>0</v>
       </c>
       <c r="AG45" s="1">
         <v>0</v>
@@ -3304,7 +3310,7 @@
     </row>
     <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -3343,7 +3349,7 @@
     </row>
     <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -3382,7 +3388,7 @@
     </row>
     <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -3421,8 +3427,9 @@
     </row>
     <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>72</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
@@ -3460,8 +3467,9 @@
     </row>
     <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>73</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
@@ -3499,7 +3507,7 @@
     </row>
     <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -3539,7 +3547,7 @@
     </row>
     <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
@@ -3579,7 +3587,7 @@
     </row>
     <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
@@ -3619,7 +3627,7 @@
     </row>
     <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
@@ -3659,8 +3667,9 @@
     </row>
     <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>78</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
@@ -3699,8 +3708,9 @@
     </row>
     <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>79</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
@@ -3739,7 +3749,7 @@
     </row>
     <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
@@ -3780,7 +3790,7 @@
     </row>
     <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
@@ -3821,7 +3831,7 @@
     </row>
     <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
@@ -3862,8 +3872,9 @@
     </row>
     <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>83</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
@@ -3903,8 +3914,9 @@
     </row>
     <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>84</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
@@ -3944,8 +3956,9 @@
     </row>
     <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>86</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
@@ -3986,8 +3999,9 @@
     </row>
     <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>87</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
@@ -4028,7 +4042,7 @@
     </row>
     <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
@@ -4071,7 +4085,7 @@
     </row>
     <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
@@ -4114,21 +4128,37 @@
     </row>
     <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>90</v>
-      </c>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1"/>
-      <c r="W66" s="1"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="1"/>
-      <c r="Z66" s="1"/>
-      <c r="AA66" s="1"/>
-      <c r="AB66" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="1">
+        <v>0</v>
+      </c>
+      <c r="X66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="1">
+        <v>0</v>
+      </c>
       <c r="AC66" s="1">
         <v>0</v>
       </c>
-      <c r="AD66" s="1">
-        <v>0</v>
+      <c r="AD66">
+        <v>15</v>
       </c>
       <c r="AE66" s="1">
         <v>0</v>
@@ -4136,17 +4166,17 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH66" s="1">
-        <v>0</v>
+      <c r="AG66">
+        <v>6</v>
+      </c>
+      <c r="AH66">
+        <v>15</v>
       </c>
       <c r="AI66" s="1">
         <v>0</v>
       </c>
-      <c r="AJ66" s="1">
-        <v>0</v>
+      <c r="AJ66">
+        <v>12</v>
       </c>
       <c r="AK66" s="1">
         <v>0</v>
@@ -4157,8 +4187,9 @@
     </row>
     <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>91</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
@@ -4200,37 +4231,22 @@
     </row>
     <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>92</v>
-      </c>
-      <c r="U68" s="1">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1">
-        <v>0</v>
-      </c>
-      <c r="W68" s="1">
-        <v>0</v>
-      </c>
-      <c r="X68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB68" s="1">
-        <v>0</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
       <c r="AC68" s="1">
         <v>0</v>
       </c>
-      <c r="AD68">
-        <v>15</v>
+      <c r="AD68" s="1">
+        <v>0</v>
       </c>
       <c r="AE68" s="1">
         <v>0</v>
@@ -4238,17 +4254,17 @@
       <c r="AF68" s="1">
         <v>0</v>
       </c>
-      <c r="AG68">
-        <v>6</v>
-      </c>
-      <c r="AH68">
-        <v>15</v>
+      <c r="AG68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="1">
+        <v>0</v>
       </c>
       <c r="AI68" s="1">
         <v>0</v>
       </c>
-      <c r="AJ68">
-        <v>12</v>
+      <c r="AJ68" s="1">
+        <v>0</v>
       </c>
       <c r="AK68" s="1">
         <v>0</v>
@@ -4259,7 +4275,7 @@
     </row>
     <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
@@ -4303,7 +4319,7 @@
     </row>
     <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
@@ -4347,7 +4363,7 @@
     </row>
     <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
@@ -4391,8 +4407,9 @@
     </row>
     <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>96</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="S72" s="1"/>
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
@@ -4435,8 +4452,9 @@
     </row>
     <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>97</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="S73" s="1"/>
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
@@ -4479,7 +4497,7 @@
     </row>
     <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
@@ -4524,7 +4542,7 @@
     </row>
     <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
@@ -4569,7 +4587,7 @@
     </row>
     <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
@@ -4614,8 +4632,9 @@
     </row>
     <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>101</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
@@ -4659,8 +4678,9 @@
     </row>
     <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>102</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -4704,8 +4724,9 @@
     </row>
     <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>103</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
@@ -4750,8 +4771,9 @@
     </row>
     <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>104</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
@@ -4796,7 +4818,7 @@
     </row>
     <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
@@ -4843,7 +4865,7 @@
     </row>
     <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
@@ -4890,7 +4912,7 @@
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
@@ -4937,8 +4959,9 @@
     </row>
     <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>108</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
@@ -4984,8 +5007,9 @@
     </row>
     <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>109</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
@@ -5031,7 +5055,7 @@
     </row>
     <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
@@ -5079,7 +5103,7 @@
     </row>
     <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
@@ -5127,8 +5151,9 @@
     </row>
     <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>112</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
@@ -5175,8 +5200,9 @@
     </row>
     <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>113</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
@@ -5223,7 +5249,7 @@
     </row>
     <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
@@ -5272,7 +5298,7 @@
     </row>
     <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
@@ -5321,7 +5347,7 @@
     </row>
     <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
@@ -5370,8 +5396,9 @@
     </row>
     <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>117</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
@@ -5419,8 +5446,9 @@
     </row>
     <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>118</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N94" s="1"/>
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
@@ -5468,7 +5496,7 @@
     </row>
     <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
@@ -5518,7 +5546,7 @@
     </row>
     <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
@@ -5568,7 +5596,7 @@
     </row>
     <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
@@ -5618,8 +5646,9 @@
     </row>
     <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>122</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
@@ -5668,8 +5697,9 @@
     </row>
     <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>123</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
@@ -5718,7 +5748,7 @@
     </row>
     <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
@@ -5769,7 +5799,7 @@
     </row>
     <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
@@ -5820,8 +5850,9 @@
     </row>
     <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>126</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
@@ -5871,8 +5902,9 @@
     </row>
     <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>127</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
@@ -5922,8 +5954,9 @@
     </row>
     <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>128</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
@@ -5974,8 +6007,9 @@
     </row>
     <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>129</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -6026,7 +6060,7 @@
     </row>
     <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -6079,8 +6113,9 @@
     </row>
     <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>131</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
@@ -6132,8 +6167,9 @@
     </row>
     <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>132</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
@@ -6185,7 +6221,7 @@
     </row>
     <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
@@ -6239,8 +6275,9 @@
     </row>
     <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>134</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -6293,8 +6330,9 @@
     </row>
     <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>135</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -6347,7 +6385,7 @@
     </row>
     <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6402,8 +6440,9 @@
     </row>
     <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>137</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
@@ -6457,8 +6496,9 @@
     </row>
     <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>138</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
@@ -6512,8 +6552,9 @@
     </row>
     <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>139</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -6568,8 +6609,9 @@
     </row>
     <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>140</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -6624,7 +6666,7 @@
     </row>
     <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
@@ -6681,8 +6723,9 @@
     </row>
     <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>142</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -6738,8 +6781,9 @@
     </row>
     <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>143</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -6795,7 +6839,7 @@
     </row>
     <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
@@ -6853,8 +6897,9 @@
     </row>
     <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>145</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -6911,8 +6956,9 @@
     </row>
     <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>146</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -6969,7 +7015,7 @@
     </row>
     <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
@@ -7028,8 +7074,9 @@
     </row>
     <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>148</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -7082,125 +7129,6 @@
         <v>0</v>
       </c>
       <c r="AL124" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>149</v>
-      </c>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="1"/>
-      <c r="N125" s="1"/>
-      <c r="O125" s="1"/>
-      <c r="P125" s="1"/>
-      <c r="Q125" s="1"/>
-      <c r="R125" s="1"/>
-      <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
-      <c r="U125" s="1"/>
-      <c r="V125" s="1"/>
-      <c r="W125" s="1"/>
-      <c r="X125" s="1"/>
-      <c r="Y125" s="1"/>
-      <c r="Z125" s="1"/>
-      <c r="AA125" s="1"/>
-      <c r="AB125" s="1"/>
-      <c r="AC125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL125" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>150</v>
-      </c>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-      <c r="N126" s="1"/>
-      <c r="O126" s="1"/>
-      <c r="P126" s="1"/>
-      <c r="Q126" s="1"/>
-      <c r="R126" s="1"/>
-      <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
-      <c r="U126" s="1"/>
-      <c r="V126" s="1"/>
-      <c r="W126" s="1"/>
-      <c r="X126" s="1"/>
-      <c r="Y126" s="1"/>
-      <c r="Z126" s="1"/>
-      <c r="AA126" s="1"/>
-      <c r="AB126" s="1"/>
-      <c r="AC126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL126" s="1">
         <v>0</v>
       </c>
     </row>
@@ -9317,11 +9245,924 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5463DBD5-1047-4E7D-B3B5-A719C2F7680D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:S2)</f>
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B21" si="0">SUM(C3:S3)</f>
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>0</v>
       </c>
     </row>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6784A2D-06EB-446A-860B-507FC7810C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1105F070-3DDB-470C-AF6B-C71CA1CB2E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="4" activeTab="11" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="11" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -1602,13 +1602,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
   <dimension ref="A1:AL124"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>67</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>68</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>69</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>70</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>71</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>73</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>81</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>82</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>84</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>86</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>88</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>89</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>90</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>91</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>92</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>93</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>95</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>96</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>97</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>98</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>99</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>100</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>102</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>103</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>104</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>105</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>107</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>108</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>109</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>110</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>111</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>112</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>113</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>114</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>115</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>116</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>117</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>118</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>119</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>121</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>123</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>124</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>125</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>126</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>127</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>128</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>129</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>130</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>131</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>132</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>133</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>134</v>
       </c>
@@ -6219,7 +6219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>135</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>136</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>137</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>138</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>140</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>141</v>
       </c>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>142</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>143</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>144</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>145</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>146</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>147</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>148</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>149</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>150</v>
       </c>
@@ -7141,26 +7141,26 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7330,7 +7330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -7957,7 +7957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -8136,30 +8136,30 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC06B72-571E-40C4-AD69-3294909EA05A}">
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -8818,7 +8818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -9058,7 +9058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -9246,28 +9246,28 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5463DBD5-1047-4E7D-B3B5-A719C2F7680D}">
   <dimension ref="A1:S21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9326,13 +9326,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>SUM(C2:S2)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -9367,14 +9367,17 @@
       <c r="M2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B21" si="0">SUM(C3:S3)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -9409,14 +9412,17 @@
       <c r="M3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -9451,14 +9457,17 @@
       <c r="M4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -9493,14 +9502,17 @@
       <c r="M5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -9535,14 +9547,17 @@
       <c r="M6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -9577,14 +9592,17 @@
       <c r="M7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -9619,14 +9637,17 @@
       <c r="M8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -9661,14 +9682,17 @@
       <c r="M9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -9703,14 +9727,17 @@
       <c r="M10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -9745,14 +9772,17 @@
       <c r="M11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -9787,14 +9817,17 @@
       <c r="M12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -9829,14 +9862,17 @@
       <c r="M13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -9871,14 +9907,17 @@
       <c r="M14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -9913,8 +9952,11 @@
       <c r="M15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -9955,14 +9997,17 @@
       <c r="M16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -9997,8 +10042,11 @@
       <c r="M17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -10039,14 +10087,17 @@
       <c r="M18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -10081,14 +10132,17 @@
       <c r="M19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -10123,14 +10177,17 @@
       <c r="M20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>64</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -10164,6 +10221,9 @@
       </c>
       <c r="M21">
         <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10174,15 +10234,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7053FD00-70E4-44ED-874D-48591AC61FE1}">
   <dimension ref="A1:S24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10241,7 +10301,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10250,7 +10310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10259,7 +10319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10268,7 +10328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10277,7 +10337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10286,7 +10346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -10295,7 +10355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -10304,7 +10364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -10313,7 +10373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -10322,7 +10382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -10331,7 +10391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -10340,7 +10400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -10349,7 +10409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -10358,7 +10418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -10367,7 +10427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -10376,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -10385,7 +10445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -10394,7 +10454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -10403,7 +10463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -10412,7 +10472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -10421,7 +10481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -10430,7 +10490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -10439,7 +10499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -10456,13 +10516,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10470,122 +10530,122 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -10598,12 +10658,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E80DB57-1D34-4995-8AA7-BD186A2BDBE8}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10611,127 +10671,127 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -10744,137 +10804,137 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F0FCB7-825F-41B0-8DBE-275FB691B4D1}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -10887,147 +10947,147 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C60C079E-583C-4AF5-A6A9-C3E86F60AFD7}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -11040,137 +11100,137 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C6E86-EC8A-4EA5-A30B-4A7F0858E0A5}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -11183,122 +11243,122 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5342EC0-9A20-4134-BF81-DC6CEEC14B92}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -11311,16 +11371,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EC39A2-025A-41B3-9C60-22F202BB8868}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11376,7 +11436,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11441,137 +11501,137 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F76B976-1DE3-4828-AFA3-C2C8CE6A8C8D}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>92</v>
       </c>
@@ -11584,147 +11644,147 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD15434-4874-452F-8199-FC863C296E8B}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -11737,152 +11797,152 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B951F07-E9BC-4825-9AA7-DCA2D6A9E9B8}">
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -11895,137 +11955,137 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED86059-0F40-42A6-AE6A-E4A8243B3C21}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -12038,127 +12098,127 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828EF67-0DDF-4C73-BB7C-135261ED3818}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -12171,127 +12231,127 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D05EA9-09C8-45DF-9887-5028388B0199}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>113</v>
       </c>
@@ -12304,117 +12364,117 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB2F14C-4266-4398-862F-517EC6F2BF68}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -12427,132 +12487,132 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9081B27-A4FF-4FDB-A545-8BEAAEB98497}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -12565,127 +12625,127 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D47B59A-B1BE-4472-A7E7-70223D1707FA}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -12698,112 +12758,112 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F202A74-DE9C-4BEE-9BC5-F661CBB67E18}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -12816,17 +12876,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA742C1-0B95-4CA1-8FA2-14D0BE967B15}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12882,7 +12942,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12947,112 +13007,112 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5FA89E6-064E-4CAF-91E1-B8698E14C23C}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>132</v>
       </c>
@@ -13065,127 +13125,127 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7743BE8-494B-4549-A27B-0B0C0DC916B8}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>135</v>
       </c>
@@ -13198,117 +13258,117 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56826E7E-7CC5-4FC4-AA7B-870479195203}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -13321,122 +13381,122 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C16F4FE-A52D-4398-8BE4-A0ECC46C9962}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -13449,122 +13509,122 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A16EA40-13C9-4D0C-A228-ED069B0DFCDE}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>140</v>
       </c>
@@ -13577,132 +13637,132 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C5AB-79A4-4A2A-A59C-9F1C1089C3B0}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -13716,117 +13776,117 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC85092-DD56-4DFB-A3DE-A66B323B833F}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>146</v>
       </c>
@@ -13839,122 +13899,122 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194B9004-BFC1-4A04-AEDF-CD50347CD713}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -13968,16 +14028,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D2BC23-0382-4C73-BD55-9C5BF90A5872}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14033,7 +14093,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14090,7 +14150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14147,7 +14207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -14204,7 +14264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -14269,15 +14329,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD508AD-7632-48CF-B894-9F6914C08CD8}">
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14333,7 +14393,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14390,7 +14450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14447,7 +14507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14504,7 +14564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -14561,7 +14621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -14618,7 +14678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -14675,7 +14735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -14732,7 +14792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -14797,12 +14857,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1668A00-6C37-4B7D-B869-26E922968418}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14861,7 +14921,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14921,7 +14981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14981,7 +15041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15041,7 +15101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -15101,7 +15161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -15161,7 +15221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -15221,7 +15281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -15281,7 +15341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -15341,7 +15401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -15409,12 +15469,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D405A22-72AA-4B8B-8276-187361E5AFF5}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15470,7 +15530,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15527,7 +15587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15584,7 +15644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15641,7 +15701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -15698,7 +15758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -15755,7 +15815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -15812,7 +15872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -15869,7 +15929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -15926,7 +15986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -15983,7 +16043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -16040,7 +16100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -16105,12 +16165,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16169,7 +16229,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16229,7 +16289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16289,7 +16349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -16349,7 +16409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -16409,7 +16469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -16469,7 +16529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -16529,7 +16589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -16589,7 +16649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -16649,7 +16709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -16709,7 +16769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -16769,7 +16829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -16829,7 +16889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -16889,7 +16949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -16957,14 +17017,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6443FC8D-E56E-407E-83EA-E01E6A3300AE}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -17020,7 +17080,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -17077,7 +17137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -17134,7 +17194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -17191,7 +17251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -17248,7 +17308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -17305,7 +17365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -17362,7 +17422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -17419,7 +17479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -17476,7 +17536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -17533,7 +17593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -17590,7 +17650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -17647,7 +17707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -17704,7 +17764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>68</v>
       </c>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1105F070-3DDB-470C-AF6B-C71CA1CB2E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF884681-884A-4F04-A19D-4184EF2DF36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="11" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -1602,13 +1602,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
   <dimension ref="A1:AL124"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1721,9 +1721,12 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>17</v>
       </c>
       <c r="AC2">
         <v>17</v>
@@ -1756,10 +1759,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AB3">
+        <v>17</v>
+      </c>
       <c r="AC3">
         <v>17</v>
       </c>
@@ -1791,10 +1797,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="AB4">
+        <v>16</v>
+      </c>
       <c r="AC4" s="1">
         <v>0</v>
       </c>
@@ -1826,10 +1835,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AB5">
+        <v>17</v>
+      </c>
       <c r="AC5">
         <v>17</v>
       </c>
@@ -1861,10 +1873,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
+      <c r="AB6">
+        <v>17</v>
+      </c>
       <c r="AC6" s="1">
         <v>0</v>
       </c>
@@ -1896,10 +1911,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AB7">
+        <v>17</v>
+      </c>
       <c r="AC7">
         <v>17</v>
       </c>
@@ -1931,11 +1949,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="AB8" s="1"/>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
       <c r="AC8" s="1">
         <v>0</v>
       </c>
@@ -1967,10 +1987,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AB9">
+        <v>17</v>
+      </c>
       <c r="AC9">
         <v>16</v>
       </c>
@@ -2002,10 +2025,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AB10">
+        <v>17</v>
+      </c>
       <c r="AC10">
         <v>17</v>
       </c>
@@ -2037,10 +2063,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AB11">
+        <v>17</v>
+      </c>
       <c r="AC11" s="1">
         <v>0</v>
       </c>
@@ -2072,10 +2101,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="AB12">
+        <v>17</v>
+      </c>
       <c r="AC12">
         <v>17</v>
       </c>
@@ -2107,10 +2139,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AB13">
+        <v>17</v>
+      </c>
       <c r="AC13">
         <v>17</v>
       </c>
@@ -2142,11 +2177,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="AB14" s="1"/>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
       <c r="AC14" s="1">
         <v>0</v>
       </c>
@@ -2178,10 +2215,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AB15">
+        <v>17</v>
+      </c>
       <c r="AC15">
         <v>17</v>
       </c>
@@ -2213,10 +2253,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AB16">
+        <v>13</v>
+      </c>
       <c r="AC16">
         <v>16</v>
       </c>
@@ -2248,10 +2291,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AB17">
+        <v>16</v>
+      </c>
       <c r="AC17">
         <v>16</v>
       </c>
@@ -2283,11 +2329,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="AB18" s="1"/>
+      <c r="AB18" s="1">
+        <v>0</v>
+      </c>
       <c r="AC18" s="1">
         <v>0</v>
       </c>
@@ -2319,11 +2367,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>85</v>
       </c>
-      <c r="AB19" s="1"/>
+      <c r="AB19" s="1">
+        <v>0</v>
+      </c>
       <c r="AC19" s="1">
         <v>0</v>
       </c>
@@ -2355,10 +2405,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="AB20">
+        <v>3</v>
+      </c>
       <c r="AC20" s="1">
         <v>0</v>
       </c>
@@ -2390,10 +2443,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="AB21">
+        <v>17</v>
+      </c>
       <c r="AC21" s="1">
         <v>0</v>
       </c>
@@ -2425,10 +2481,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AB22">
+        <v>15</v>
+      </c>
       <c r="AC22">
         <v>17</v>
       </c>
@@ -2460,10 +2519,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
       <c r="AC23">
         <v>15</v>
       </c>
@@ -2495,11 +2557,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="AB24" s="1"/>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
       <c r="AC24" s="1">
         <v>0</v>
       </c>
@@ -2531,10 +2595,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>16</v>
+      </c>
       <c r="AC25" s="1">
         <v>0</v>
       </c>
@@ -2566,12 +2633,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>45</v>
       </c>
       <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
+      <c r="AB26" s="1">
+        <v>0</v>
+      </c>
       <c r="AC26" s="1">
         <v>0</v>
       </c>
@@ -2603,12 +2672,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>46</v>
       </c>
       <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
+      <c r="AB27" s="1">
+        <v>0</v>
+      </c>
       <c r="AC27" s="1">
         <v>0</v>
       </c>
@@ -2640,10 +2711,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AB28">
+        <v>17</v>
+      </c>
       <c r="AC28">
         <v>17</v>
       </c>
@@ -2675,12 +2749,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
+      <c r="AB29" s="1">
+        <v>0</v>
+      </c>
       <c r="AC29" s="1">
         <v>0</v>
       </c>
@@ -2712,12 +2788,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
+      <c r="AB30" s="1">
+        <v>0</v>
+      </c>
       <c r="AC30" s="1">
         <v>0</v>
       </c>
@@ -2749,10 +2827,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>53</v>
       </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
       <c r="AC31">
         <v>17</v>
       </c>
@@ -2784,12 +2865,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>57</v>
       </c>
       <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
+      <c r="AB32" s="1">
+        <v>0</v>
+      </c>
       <c r="AC32" s="1">
         <v>0</v>
       </c>
@@ -2821,12 +2904,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>58</v>
       </c>
       <c r="AA33" s="1"/>
-      <c r="AB33" s="1"/>
+      <c r="AB33" s="1">
+        <v>0</v>
+      </c>
       <c r="AC33" s="1">
         <v>0</v>
       </c>
@@ -2858,12 +2943,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>59</v>
       </c>
       <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
+      <c r="AB34" s="1">
+        <v>0</v>
+      </c>
       <c r="AC34" s="1">
         <v>0</v>
       </c>
@@ -2895,12 +2982,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
       <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
+      <c r="AB35" s="1">
+        <v>0</v>
+      </c>
       <c r="AC35" s="1">
         <v>0</v>
       </c>
@@ -2932,12 +3021,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
       <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
+      <c r="AB36" s="1">
+        <v>0</v>
+      </c>
       <c r="AC36" s="1">
         <v>0</v>
       </c>
@@ -2969,13 +3060,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>62</v>
       </c>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
+      <c r="AB37" s="1">
+        <v>0</v>
+      </c>
       <c r="AC37" s="1">
         <v>0</v>
       </c>
@@ -3007,13 +3100,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>63</v>
       </c>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
+      <c r="AB38" s="1">
+        <v>0</v>
+      </c>
       <c r="AC38" s="1">
         <v>0</v>
       </c>
@@ -3045,10 +3140,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>64</v>
       </c>
+      <c r="AB39">
+        <v>2</v>
+      </c>
       <c r="AC39">
         <v>17</v>
       </c>
@@ -3080,13 +3178,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>65</v>
       </c>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
-      <c r="AB40" s="1"/>
+      <c r="AB40" s="1">
+        <v>0</v>
+      </c>
       <c r="AC40" s="1">
         <v>0</v>
       </c>
@@ -3118,13 +3218,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>66</v>
       </c>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
-      <c r="AB41" s="1"/>
+      <c r="AB41" s="1">
+        <v>0</v>
+      </c>
       <c r="AC41" s="1">
         <v>0</v>
       </c>
@@ -3156,14 +3258,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>67</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
+      <c r="AB42" s="1">
+        <v>0</v>
+      </c>
       <c r="AC42" s="1">
         <v>0</v>
       </c>
@@ -3195,10 +3299,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>68</v>
       </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
       <c r="AC43">
         <v>17</v>
       </c>
@@ -3230,14 +3337,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>69</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
+      <c r="AB44" s="1">
+        <v>0</v>
+      </c>
       <c r="AC44" s="1">
         <v>0</v>
       </c>
@@ -3269,14 +3378,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>70</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
-      <c r="AB45" s="1"/>
+      <c r="AB45" s="1">
+        <v>0</v>
+      </c>
       <c r="AC45" s="1">
         <v>0</v>
       </c>
@@ -3308,14 +3419,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>71</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
-      <c r="AB46" s="1"/>
+      <c r="AB46" s="1">
+        <v>0</v>
+      </c>
       <c r="AC46" s="1">
         <v>0</v>
       </c>
@@ -3347,14 +3460,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
-      <c r="AB47" s="1"/>
+      <c r="AB47" s="1">
+        <v>0</v>
+      </c>
       <c r="AC47" s="1">
         <v>0</v>
       </c>
@@ -3386,14 +3501,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>73</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
-      <c r="AB48" s="1"/>
+      <c r="AB48" s="1">
+        <v>0</v>
+      </c>
       <c r="AC48" s="1">
         <v>0</v>
       </c>
@@ -3425,7 +3542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -3433,7 +3550,9 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
-      <c r="AB49" s="1"/>
+      <c r="AB49" s="1">
+        <v>0</v>
+      </c>
       <c r="AC49" s="1">
         <v>0</v>
       </c>
@@ -3465,7 +3584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -3473,7 +3592,9 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
-      <c r="AB50" s="1"/>
+      <c r="AB50" s="1">
+        <v>0</v>
+      </c>
       <c r="AC50" s="1">
         <v>0</v>
       </c>
@@ -3505,7 +3626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -3513,7 +3634,9 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
-      <c r="AB51" s="1"/>
+      <c r="AB51" s="1">
+        <v>0</v>
+      </c>
       <c r="AC51" s="1">
         <v>0</v>
       </c>
@@ -3545,7 +3668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -3553,7 +3676,9 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
-      <c r="AB52" s="1"/>
+      <c r="AB52" s="1">
+        <v>0</v>
+      </c>
       <c r="AC52" s="1">
         <v>0</v>
       </c>
@@ -3585,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -3593,7 +3718,9 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
-      <c r="AB53" s="1"/>
+      <c r="AB53" s="1">
+        <v>0</v>
+      </c>
       <c r="AC53" s="1">
         <v>0</v>
       </c>
@@ -3625,7 +3752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -3633,7 +3760,9 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
-      <c r="AB54" s="1"/>
+      <c r="AB54" s="1">
+        <v>0</v>
+      </c>
       <c r="AC54" s="1">
         <v>0</v>
       </c>
@@ -3665,7 +3794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -3674,7 +3803,9 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
-      <c r="AB55" s="1"/>
+      <c r="AB55" s="1">
+        <v>0</v>
+      </c>
       <c r="AC55" s="1">
         <v>0</v>
       </c>
@@ -3706,7 +3837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>81</v>
       </c>
@@ -3715,7 +3846,9 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
-      <c r="AB56" s="1"/>
+      <c r="AB56" s="1">
+        <v>0</v>
+      </c>
       <c r="AC56" s="1">
         <v>0</v>
       </c>
@@ -3747,7 +3880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>82</v>
       </c>
@@ -3756,7 +3889,9 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
-      <c r="AB57" s="1"/>
+      <c r="AB57" s="1">
+        <v>0</v>
+      </c>
       <c r="AC57" s="1">
         <v>0</v>
       </c>
@@ -3788,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -3797,7 +3932,9 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
-      <c r="AB58" s="1"/>
+      <c r="AB58" s="1">
+        <v>0</v>
+      </c>
       <c r="AC58" s="1">
         <v>0</v>
       </c>
@@ -3829,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>84</v>
       </c>
@@ -3838,7 +3975,9 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
-      <c r="AB59" s="1"/>
+      <c r="AB59" s="1">
+        <v>0</v>
+      </c>
       <c r="AC59" s="1">
         <v>0</v>
       </c>
@@ -3870,7 +4009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>86</v>
       </c>
@@ -3880,7 +4019,9 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
-      <c r="AB60" s="1"/>
+      <c r="AB60" s="1">
+        <v>0</v>
+      </c>
       <c r="AC60" s="1">
         <v>0</v>
       </c>
@@ -3912,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -3922,7 +4063,9 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
-      <c r="AB61" s="1"/>
+      <c r="AB61" s="1">
+        <v>0</v>
+      </c>
       <c r="AC61" s="1">
         <v>0</v>
       </c>
@@ -3954,7 +4097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>88</v>
       </c>
@@ -3965,7 +4108,9 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
-      <c r="AB62" s="1"/>
+      <c r="AB62" s="1">
+        <v>0</v>
+      </c>
       <c r="AC62" s="1">
         <v>0</v>
       </c>
@@ -3997,7 +4142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>89</v>
       </c>
@@ -4008,7 +4153,9 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
-      <c r="AB63" s="1"/>
+      <c r="AB63" s="1">
+        <v>0</v>
+      </c>
       <c r="AC63" s="1">
         <v>0</v>
       </c>
@@ -4040,7 +4187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>90</v>
       </c>
@@ -4051,7 +4198,9 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
-      <c r="AB64" s="1"/>
+      <c r="AB64" s="1">
+        <v>0</v>
+      </c>
       <c r="AC64" s="1">
         <v>0</v>
       </c>
@@ -4083,7 +4232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>91</v>
       </c>
@@ -4094,7 +4243,9 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
-      <c r="AB65" s="1"/>
+      <c r="AB65" s="1">
+        <v>0</v>
+      </c>
       <c r="AC65" s="1">
         <v>0</v>
       </c>
@@ -4126,7 +4277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>92</v>
       </c>
@@ -4185,7 +4336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>93</v>
       </c>
@@ -4197,7 +4348,9 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
-      <c r="AB67" s="1"/>
+      <c r="AB67" s="1">
+        <v>0</v>
+      </c>
       <c r="AC67" s="1">
         <v>0</v>
       </c>
@@ -4229,7 +4382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -4241,7 +4394,9 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
-      <c r="AB68" s="1"/>
+      <c r="AB68" s="1">
+        <v>0</v>
+      </c>
       <c r="AC68" s="1">
         <v>0</v>
       </c>
@@ -4273,7 +4428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>95</v>
       </c>
@@ -4285,7 +4440,9 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
-      <c r="AB69" s="1"/>
+      <c r="AB69" s="1">
+        <v>0</v>
+      </c>
       <c r="AC69" s="1">
         <v>0</v>
       </c>
@@ -4317,7 +4474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>96</v>
       </c>
@@ -4329,7 +4486,9 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
-      <c r="AB70" s="1"/>
+      <c r="AB70" s="1">
+        <v>0</v>
+      </c>
       <c r="AC70" s="1">
         <v>0</v>
       </c>
@@ -4361,7 +4520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>97</v>
       </c>
@@ -4373,7 +4532,9 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
-      <c r="AB71" s="1"/>
+      <c r="AB71" s="1">
+        <v>0</v>
+      </c>
       <c r="AC71" s="1">
         <v>0</v>
       </c>
@@ -4405,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>98</v>
       </c>
@@ -4418,7 +4579,9 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
-      <c r="AB72" s="1"/>
+      <c r="AB72" s="1">
+        <v>0</v>
+      </c>
       <c r="AC72" s="1">
         <v>0</v>
       </c>
@@ -4450,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>99</v>
       </c>
@@ -4463,7 +4626,9 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
       <c r="AA73" s="1"/>
-      <c r="AB73" s="1"/>
+      <c r="AB73" s="1">
+        <v>0</v>
+      </c>
       <c r="AC73" s="1">
         <v>0</v>
       </c>
@@ -4495,7 +4660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>100</v>
       </c>
@@ -4508,7 +4673,9 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
-      <c r="AB74" s="1"/>
+      <c r="AB74" s="1">
+        <v>0</v>
+      </c>
       <c r="AC74" s="1">
         <v>0</v>
       </c>
@@ -4540,7 +4707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -4553,7 +4720,9 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
-      <c r="AB75" s="1"/>
+      <c r="AB75" s="1">
+        <v>0</v>
+      </c>
       <c r="AC75" s="1">
         <v>0</v>
       </c>
@@ -4585,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>102</v>
       </c>
@@ -4598,7 +4767,9 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
-      <c r="AB76" s="1"/>
+      <c r="AB76" s="1">
+        <v>0</v>
+      </c>
       <c r="AC76" s="1">
         <v>0</v>
       </c>
@@ -4630,7 +4801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>103</v>
       </c>
@@ -4644,7 +4815,9 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
-      <c r="AB77" s="1"/>
+      <c r="AB77" s="1">
+        <v>0</v>
+      </c>
       <c r="AC77" s="1">
         <v>0</v>
       </c>
@@ -4676,7 +4849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>104</v>
       </c>
@@ -4690,7 +4863,9 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
-      <c r="AB78" s="1"/>
+      <c r="AB78" s="1">
+        <v>0</v>
+      </c>
       <c r="AC78" s="1">
         <v>0</v>
       </c>
@@ -4722,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>105</v>
       </c>
@@ -4737,7 +4912,9 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
-      <c r="AB79" s="1"/>
+      <c r="AB79" s="1">
+        <v>0</v>
+      </c>
       <c r="AC79" s="1">
         <v>0</v>
       </c>
@@ -4769,7 +4946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -4784,7 +4961,9 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
-      <c r="AB80" s="1"/>
+      <c r="AB80" s="1">
+        <v>0</v>
+      </c>
       <c r="AC80" s="1">
         <v>0</v>
       </c>
@@ -4816,7 +4995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>107</v>
       </c>
@@ -4831,7 +5010,9 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
-      <c r="AB81" s="1"/>
+      <c r="AB81" s="1">
+        <v>0</v>
+      </c>
       <c r="AC81" s="1">
         <v>0</v>
       </c>
@@ -4863,7 +5044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>108</v>
       </c>
@@ -4878,7 +5059,9 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
       <c r="AA82" s="1"/>
-      <c r="AB82" s="1"/>
+      <c r="AB82" s="1">
+        <v>0</v>
+      </c>
       <c r="AC82" s="1">
         <v>0</v>
       </c>
@@ -4910,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>109</v>
       </c>
@@ -4925,7 +5108,9 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
       <c r="AA83" s="1"/>
-      <c r="AB83" s="1"/>
+      <c r="AB83" s="1">
+        <v>0</v>
+      </c>
       <c r="AC83" s="1">
         <v>0</v>
       </c>
@@ -4957,7 +5142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>110</v>
       </c>
@@ -4973,7 +5158,9 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
       <c r="AA84" s="1"/>
-      <c r="AB84" s="1"/>
+      <c r="AB84" s="1">
+        <v>0</v>
+      </c>
       <c r="AC84" s="1">
         <v>0</v>
       </c>
@@ -5005,7 +5192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>111</v>
       </c>
@@ -5021,7 +5208,9 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
       <c r="AA85" s="1"/>
-      <c r="AB85" s="1"/>
+      <c r="AB85" s="1">
+        <v>0</v>
+      </c>
       <c r="AC85" s="1">
         <v>0</v>
       </c>
@@ -5053,7 +5242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>112</v>
       </c>
@@ -5069,7 +5258,9 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
-      <c r="AB86" s="1"/>
+      <c r="AB86" s="1">
+        <v>0</v>
+      </c>
       <c r="AC86" s="1">
         <v>0</v>
       </c>
@@ -5101,7 +5292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>113</v>
       </c>
@@ -5117,7 +5308,9 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
       <c r="AA87" s="1"/>
-      <c r="AB87" s="1"/>
+      <c r="AB87" s="1">
+        <v>0</v>
+      </c>
       <c r="AC87" s="1">
         <v>0</v>
       </c>
@@ -5149,7 +5342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>114</v>
       </c>
@@ -5166,7 +5359,9 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
-      <c r="AB88" s="1"/>
+      <c r="AB88" s="1">
+        <v>0</v>
+      </c>
       <c r="AC88" s="1">
         <v>0</v>
       </c>
@@ -5198,7 +5393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>115</v>
       </c>
@@ -5215,7 +5410,9 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
       <c r="AA89" s="1"/>
-      <c r="AB89" s="1"/>
+      <c r="AB89" s="1">
+        <v>0</v>
+      </c>
       <c r="AC89" s="1">
         <v>0</v>
       </c>
@@ -5247,7 +5444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>116</v>
       </c>
@@ -5264,7 +5461,9 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
       <c r="AA90" s="1"/>
-      <c r="AB90" s="1"/>
+      <c r="AB90" s="1">
+        <v>0</v>
+      </c>
       <c r="AC90" s="1">
         <v>0</v>
       </c>
@@ -5296,7 +5495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>117</v>
       </c>
@@ -5313,7 +5512,9 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
       <c r="AA91" s="1"/>
-      <c r="AB91" s="1"/>
+      <c r="AB91" s="1">
+        <v>0</v>
+      </c>
       <c r="AC91" s="1">
         <v>0</v>
       </c>
@@ -5345,7 +5546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>118</v>
       </c>
@@ -5362,7 +5563,9 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
-      <c r="AB92" s="1"/>
+      <c r="AB92" s="1">
+        <v>0</v>
+      </c>
       <c r="AC92" s="1">
         <v>0</v>
       </c>
@@ -5394,7 +5597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>119</v>
       </c>
@@ -5412,7 +5615,9 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
-      <c r="AB93" s="1"/>
+      <c r="AB93" s="1">
+        <v>0</v>
+      </c>
       <c r="AC93" s="1">
         <v>0</v>
       </c>
@@ -5444,7 +5649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -5462,7 +5667,9 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
       <c r="AA94" s="1"/>
-      <c r="AB94" s="1"/>
+      <c r="AB94" s="1">
+        <v>0</v>
+      </c>
       <c r="AC94" s="1">
         <v>0</v>
       </c>
@@ -5494,7 +5701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>121</v>
       </c>
@@ -5512,7 +5719,9 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
       <c r="AA95" s="1"/>
-      <c r="AB95" s="1"/>
+      <c r="AB95" s="1">
+        <v>0</v>
+      </c>
       <c r="AC95" s="1">
         <v>0</v>
       </c>
@@ -5544,7 +5753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -5562,7 +5771,9 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
       <c r="AA96" s="1"/>
-      <c r="AB96" s="1"/>
+      <c r="AB96" s="1">
+        <v>0</v>
+      </c>
       <c r="AC96" s="1">
         <v>0</v>
       </c>
@@ -5594,7 +5805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>123</v>
       </c>
@@ -5612,7 +5823,9 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
-      <c r="AB97" s="1"/>
+      <c r="AB97" s="1">
+        <v>0</v>
+      </c>
       <c r="AC97" s="1">
         <v>0</v>
       </c>
@@ -5644,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>124</v>
       </c>
@@ -5663,7 +5876,9 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
       <c r="AA98" s="1"/>
-      <c r="AB98" s="1"/>
+      <c r="AB98" s="1">
+        <v>0</v>
+      </c>
       <c r="AC98" s="1">
         <v>0</v>
       </c>
@@ -5695,7 +5910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>125</v>
       </c>
@@ -5714,7 +5929,9 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
-      <c r="AB99" s="1"/>
+      <c r="AB99" s="1">
+        <v>0</v>
+      </c>
       <c r="AC99" s="1">
         <v>0</v>
       </c>
@@ -5746,7 +5963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>126</v>
       </c>
@@ -5765,7 +5982,9 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
-      <c r="AB100" s="1"/>
+      <c r="AB100" s="1">
+        <v>0</v>
+      </c>
       <c r="AC100" s="1">
         <v>0</v>
       </c>
@@ -5797,7 +6016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>127</v>
       </c>
@@ -5816,7 +6035,9 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
-      <c r="AB101" s="1"/>
+      <c r="AB101" s="1">
+        <v>0</v>
+      </c>
       <c r="AC101" s="1">
         <v>0</v>
       </c>
@@ -5848,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>128</v>
       </c>
@@ -5868,7 +6089,9 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
-      <c r="AB102" s="1"/>
+      <c r="AB102" s="1">
+        <v>0</v>
+      </c>
       <c r="AC102" s="1">
         <v>0</v>
       </c>
@@ -5900,7 +6123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>129</v>
       </c>
@@ -5920,7 +6143,9 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
-      <c r="AB103" s="1"/>
+      <c r="AB103" s="1">
+        <v>0</v>
+      </c>
       <c r="AC103" s="1">
         <v>0</v>
       </c>
@@ -5952,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>130</v>
       </c>
@@ -5973,7 +6198,9 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
       <c r="AA104" s="1"/>
-      <c r="AB104" s="1"/>
+      <c r="AB104" s="1">
+        <v>0</v>
+      </c>
       <c r="AC104" s="1">
         <v>0</v>
       </c>
@@ -6005,7 +6232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>131</v>
       </c>
@@ -6026,7 +6253,9 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
-      <c r="AB105" s="1"/>
+      <c r="AB105" s="1">
+        <v>0</v>
+      </c>
       <c r="AC105" s="1">
         <v>0</v>
       </c>
@@ -6058,7 +6287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>132</v>
       </c>
@@ -6079,7 +6308,9 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
       <c r="AA106" s="1"/>
-      <c r="AB106" s="1"/>
+      <c r="AB106" s="1">
+        <v>0</v>
+      </c>
       <c r="AC106" s="1">
         <v>0</v>
       </c>
@@ -6111,7 +6342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>133</v>
       </c>
@@ -6133,7 +6364,9 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
-      <c r="AB107" s="1"/>
+      <c r="AB107" s="1">
+        <v>0</v>
+      </c>
       <c r="AC107" s="1">
         <v>0</v>
       </c>
@@ -6165,7 +6398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>134</v>
       </c>
@@ -6187,7 +6420,9 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
-      <c r="AB108" s="1"/>
+      <c r="AB108" s="1">
+        <v>0</v>
+      </c>
       <c r="AC108" s="1">
         <v>0</v>
       </c>
@@ -6219,7 +6454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>135</v>
       </c>
@@ -6241,7 +6476,9 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
-      <c r="AB109" s="1"/>
+      <c r="AB109" s="1">
+        <v>0</v>
+      </c>
       <c r="AC109" s="1">
         <v>0</v>
       </c>
@@ -6273,7 +6510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>136</v>
       </c>
@@ -6296,7 +6533,9 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
-      <c r="AB110" s="1"/>
+      <c r="AB110" s="1">
+        <v>0</v>
+      </c>
       <c r="AC110" s="1">
         <v>0</v>
       </c>
@@ -6328,7 +6567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>137</v>
       </c>
@@ -6351,7 +6590,9 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
-      <c r="AB111" s="1"/>
+      <c r="AB111" s="1">
+        <v>0</v>
+      </c>
       <c r="AC111" s="1">
         <v>0</v>
       </c>
@@ -6383,7 +6624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>138</v>
       </c>
@@ -6406,7 +6647,9 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
-      <c r="AB112" s="1"/>
+      <c r="AB112" s="1">
+        <v>0</v>
+      </c>
       <c r="AC112" s="1">
         <v>0</v>
       </c>
@@ -6438,7 +6681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -6462,7 +6705,9 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
-      <c r="AB113" s="1"/>
+      <c r="AB113" s="1">
+        <v>0</v>
+      </c>
       <c r="AC113" s="1">
         <v>0</v>
       </c>
@@ -6494,7 +6739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>140</v>
       </c>
@@ -6518,7 +6763,9 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
-      <c r="AB114" s="1"/>
+      <c r="AB114" s="1">
+        <v>0</v>
+      </c>
       <c r="AC114" s="1">
         <v>0</v>
       </c>
@@ -6550,7 +6797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>141</v>
       </c>
@@ -6575,7 +6822,9 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
-      <c r="AB115" s="1"/>
+      <c r="AB115" s="1">
+        <v>0</v>
+      </c>
       <c r="AC115" s="1">
         <v>0</v>
       </c>
@@ -6607,7 +6856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>142</v>
       </c>
@@ -6632,7 +6881,9 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
-      <c r="AB116" s="1"/>
+      <c r="AB116" s="1">
+        <v>0</v>
+      </c>
       <c r="AC116" s="1">
         <v>0</v>
       </c>
@@ -6664,7 +6915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>143</v>
       </c>
@@ -6689,7 +6940,9 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
-      <c r="AB117" s="1"/>
+      <c r="AB117" s="1">
+        <v>0</v>
+      </c>
       <c r="AC117" s="1">
         <v>0</v>
       </c>
@@ -6721,7 +6974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>144</v>
       </c>
@@ -6747,7 +7000,9 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
-      <c r="AB118" s="1"/>
+      <c r="AB118" s="1">
+        <v>0</v>
+      </c>
       <c r="AC118" s="1">
         <v>0</v>
       </c>
@@ -6779,7 +7034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>145</v>
       </c>
@@ -6805,7 +7060,9 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
-      <c r="AB119" s="1"/>
+      <c r="AB119" s="1">
+        <v>0</v>
+      </c>
       <c r="AC119" s="1">
         <v>0</v>
       </c>
@@ -6837,7 +7094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>146</v>
       </c>
@@ -6863,7 +7120,9 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
-      <c r="AB120" s="1"/>
+      <c r="AB120" s="1">
+        <v>0</v>
+      </c>
       <c r="AC120" s="1">
         <v>0</v>
       </c>
@@ -6895,7 +7154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>147</v>
       </c>
@@ -6922,7 +7181,9 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
-      <c r="AB121" s="1"/>
+      <c r="AB121" s="1">
+        <v>0</v>
+      </c>
       <c r="AC121" s="1">
         <v>0</v>
       </c>
@@ -6954,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>148</v>
       </c>
@@ -6981,7 +7242,9 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
-      <c r="AB122" s="1"/>
+      <c r="AB122" s="1">
+        <v>0</v>
+      </c>
       <c r="AC122" s="1">
         <v>0</v>
       </c>
@@ -7013,7 +7276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>149</v>
       </c>
@@ -7040,7 +7303,9 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
-      <c r="AB123" s="1"/>
+      <c r="AB123" s="1">
+        <v>0</v>
+      </c>
       <c r="AC123" s="1">
         <v>0</v>
       </c>
@@ -7072,7 +7337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>150</v>
       </c>
@@ -7100,7 +7365,9 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
-      <c r="AB124" s="1"/>
+      <c r="AB124" s="1">
+        <v>0</v>
+      </c>
       <c r="AC124" s="1">
         <v>0</v>
       </c>
@@ -7141,26 +7408,26 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7216,7 +7483,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7273,7 +7540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7330,7 +7597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -7387,7 +7654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -7444,7 +7711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -7501,7 +7768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -7558,7 +7825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -7615,7 +7882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -7672,7 +7939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -7729,7 +7996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7786,7 +8053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -7843,7 +8110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7900,7 +8167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -7957,7 +8224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -8014,7 +8281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -8071,7 +8338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -8136,30 +8403,30 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC06B72-571E-40C4-AD69-3294909EA05A}">
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8218,7 +8485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8278,7 +8545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8338,7 +8605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -8398,7 +8665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -8458,7 +8725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8518,7 +8785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -8578,7 +8845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -8638,7 +8905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -8698,7 +8965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -8758,7 +9025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -8818,7 +9085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -8878,7 +9145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -8938,7 +9205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -8998,7 +9265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -9058,7 +9325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -9118,7 +9385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -9178,7 +9445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -9246,28 +9513,28 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5463DBD5-1047-4E7D-B3B5-A719C2F7680D}">
   <dimension ref="A1:S21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9326,13 +9593,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>SUM(C2:S2)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -9370,14 +9637,29 @@
       <c r="N2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B21" si="0">SUM(C3:S3)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -9415,14 +9697,29 @@
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -9460,14 +9757,29 @@
       <c r="N4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -9505,14 +9817,29 @@
       <c r="N5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -9550,14 +9877,29 @@
       <c r="N6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -9595,14 +9937,29 @@
       <c r="N7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -9640,14 +9997,29 @@
       <c r="N8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -9685,14 +10057,29 @@
       <c r="N9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -9730,14 +10117,29 @@
       <c r="N10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -9775,14 +10177,29 @@
       <c r="N11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -9820,14 +10237,29 @@
       <c r="N12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -9865,14 +10297,29 @@
       <c r="N13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -9910,14 +10357,29 @@
       <c r="N14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -9955,14 +10417,29 @@
       <c r="N15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -10000,14 +10477,29 @@
       <c r="N16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -10045,14 +10537,29 @@
       <c r="N17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -10090,14 +10597,29 @@
       <c r="N18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -10135,14 +10657,29 @@
       <c r="N19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -10180,8 +10717,23 @@
       <c r="N20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -10224,6 +10776,21 @@
       </c>
       <c r="N21">
         <v>1</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10234,15 +10801,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7053FD00-70E4-44ED-874D-48591AC61FE1}">
   <dimension ref="A1:S24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10301,7 +10868,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10310,7 +10877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10319,7 +10886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10328,7 +10895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10337,7 +10904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10346,7 +10913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -10355,7 +10922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -10364,7 +10931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -10373,7 +10940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -10382,7 +10949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -10391,7 +10958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -10400,7 +10967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -10409,7 +10976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -10418,7 +10985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -10427,7 +10994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -10436,7 +11003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -10445,7 +11012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -10454,7 +11021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -10463,7 +11030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -10472,7 +11039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -10481,7 +11048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -10490,7 +11057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -10499,7 +11066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -10516,13 +11083,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10530,122 +11097,122 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -10658,12 +11225,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E80DB57-1D34-4995-8AA7-BD186A2BDBE8}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10671,127 +11238,127 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -10804,137 +11371,137 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F0FCB7-825F-41B0-8DBE-275FB691B4D1}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -10947,147 +11514,147 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C60C079E-583C-4AF5-A6A9-C3E86F60AFD7}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -11100,137 +11667,137 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C6E86-EC8A-4EA5-A30B-4A7F0858E0A5}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -11243,122 +11810,122 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5342EC0-9A20-4134-BF81-DC6CEEC14B92}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -11371,16 +11938,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EC39A2-025A-41B3-9C60-22F202BB8868}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11436,7 +12003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11501,137 +12068,137 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F76B976-1DE3-4828-AFA3-C2C8CE6A8C8D}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>92</v>
       </c>
@@ -11644,147 +12211,147 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD15434-4874-452F-8199-FC863C296E8B}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -11797,152 +12364,152 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B951F07-E9BC-4825-9AA7-DCA2D6A9E9B8}">
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -11955,137 +12522,137 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED86059-0F40-42A6-AE6A-E4A8243B3C21}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -12098,127 +12665,127 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828EF67-0DDF-4C73-BB7C-135261ED3818}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -12231,127 +12798,127 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D05EA9-09C8-45DF-9887-5028388B0199}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>113</v>
       </c>
@@ -12364,117 +12931,117 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB2F14C-4266-4398-862F-517EC6F2BF68}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -12487,132 +13054,132 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9081B27-A4FF-4FDB-A545-8BEAAEB98497}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -12625,127 +13192,127 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D47B59A-B1BE-4472-A7E7-70223D1707FA}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -12758,112 +13325,112 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F202A74-DE9C-4BEE-9BC5-F661CBB67E18}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -12876,17 +13443,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA742C1-0B95-4CA1-8FA2-14D0BE967B15}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12942,7 +13509,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13007,112 +13574,112 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5FA89E6-064E-4CAF-91E1-B8698E14C23C}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>132</v>
       </c>
@@ -13125,127 +13692,127 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7743BE8-494B-4549-A27B-0B0C0DC916B8}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>135</v>
       </c>
@@ -13258,117 +13825,117 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56826E7E-7CC5-4FC4-AA7B-870479195203}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -13381,122 +13948,122 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C16F4FE-A52D-4398-8BE4-A0ECC46C9962}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -13509,122 +14076,122 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A16EA40-13C9-4D0C-A228-ED069B0DFCDE}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>140</v>
       </c>
@@ -13637,132 +14204,132 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C5AB-79A4-4A2A-A59C-9F1C1089C3B0}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -13776,117 +14343,117 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC85092-DD56-4DFB-A3DE-A66B323B833F}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>146</v>
       </c>
@@ -13899,122 +14466,122 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194B9004-BFC1-4A04-AEDF-CD50347CD713}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -14028,16 +14595,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D2BC23-0382-4C73-BD55-9C5BF90A5872}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14093,7 +14660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14150,7 +14717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14207,7 +14774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -14264,7 +14831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -14329,15 +14896,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD508AD-7632-48CF-B894-9F6914C08CD8}">
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14393,7 +14960,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14450,7 +15017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14507,7 +15074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14564,7 +15131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -14621,7 +15188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -14678,7 +15245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -14735,7 +15302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -14792,7 +15359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -14857,12 +15424,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1668A00-6C37-4B7D-B869-26E922968418}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14921,7 +15488,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14981,7 +15548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15041,7 +15608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15101,7 +15668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -15161,7 +15728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -15221,7 +15788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -15281,7 +15848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -15341,7 +15908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -15401,7 +15968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -15469,12 +16036,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D405A22-72AA-4B8B-8276-187361E5AFF5}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15530,7 +16097,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15587,7 +16154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15644,7 +16211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15701,7 +16268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -15758,7 +16325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -15815,7 +16382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -15872,7 +16439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -15929,7 +16496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -15986,7 +16553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -16043,7 +16610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -16100,7 +16667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -16165,12 +16732,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16229,7 +16796,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16289,7 +16856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16349,7 +16916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -16409,7 +16976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -16469,7 +17036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -16529,7 +17096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -16589,7 +17156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -16649,7 +17216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -16709,7 +17276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -16769,7 +17336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -16829,7 +17396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -16889,7 +17456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -16949,7 +17516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -17017,14 +17584,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6443FC8D-E56E-407E-83EA-E01E6A3300AE}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -17080,7 +17647,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -17137,7 +17704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -17194,7 +17761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -17251,7 +17818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -17308,7 +17875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -17365,7 +17932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -17422,7 +17989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -17479,7 +18046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -17536,7 +18103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -17593,7 +18160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -17650,7 +18217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -17707,7 +18274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -17764,7 +18331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF884681-884A-4F04-A19D-4184EF2DF36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB09F56D-2401-4DF1-8D83-BC50326EE30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="6" activeTab="13" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1725,6 +1725,12 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="Z2">
+        <v>16</v>
+      </c>
+      <c r="AA2">
+        <v>17</v>
+      </c>
       <c r="AB2">
         <v>17</v>
       </c>
@@ -1763,6 +1769,12 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="Z3">
+        <v>16</v>
+      </c>
+      <c r="AA3">
+        <v>16</v>
+      </c>
       <c r="AB3">
         <v>17</v>
       </c>
@@ -1801,6 +1813,12 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="Z4">
+        <v>16</v>
+      </c>
+      <c r="AA4">
+        <v>17</v>
+      </c>
       <c r="AB4">
         <v>16</v>
       </c>
@@ -1839,6 +1857,12 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="Z5">
+        <v>16</v>
+      </c>
+      <c r="AA5">
+        <v>17</v>
+      </c>
       <c r="AB5">
         <v>17</v>
       </c>
@@ -1877,6 +1901,12 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
+      <c r="Z6">
+        <v>16</v>
+      </c>
+      <c r="AA6">
+        <v>17</v>
+      </c>
       <c r="AB6">
         <v>17</v>
       </c>
@@ -1915,6 +1945,12 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="Z7">
+        <v>15</v>
+      </c>
+      <c r="AA7">
+        <v>17</v>
+      </c>
       <c r="AB7">
         <v>17</v>
       </c>
@@ -1953,6 +1989,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
+      <c r="AA8">
+        <v>16</v>
+      </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
@@ -1991,6 +2030,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AA9">
+        <v>17</v>
+      </c>
       <c r="AB9">
         <v>17</v>
       </c>
@@ -2029,6 +2071,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AA10">
+        <v>17</v>
+      </c>
       <c r="AB10">
         <v>17</v>
       </c>
@@ -2067,6 +2112,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AA11">
+        <v>17</v>
+      </c>
       <c r="AB11">
         <v>17</v>
       </c>
@@ -2105,6 +2153,12 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="Z12">
+        <v>15</v>
+      </c>
+      <c r="AA12">
+        <v>17</v>
+      </c>
       <c r="AB12">
         <v>17</v>
       </c>
@@ -2143,6 +2197,12 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="Z13">
+        <v>16</v>
+      </c>
+      <c r="AA13">
+        <v>17</v>
+      </c>
       <c r="AB13">
         <v>17</v>
       </c>
@@ -2181,6 +2241,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="AA14">
+        <v>17</v>
+      </c>
       <c r="AB14" s="1">
         <v>0</v>
       </c>
@@ -2219,6 +2282,12 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="Z15">
+        <v>16</v>
+      </c>
+      <c r="AA15">
+        <v>16</v>
+      </c>
       <c r="AB15">
         <v>17</v>
       </c>
@@ -2257,6 +2326,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AA16">
+        <v>17</v>
+      </c>
       <c r="AB16">
         <v>13</v>
       </c>
@@ -2295,6 +2367,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AA17">
+        <v>17</v>
+      </c>
       <c r="AB17">
         <v>16</v>
       </c>
@@ -2333,6 +2408,12 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
+      <c r="Z18">
+        <v>16</v>
+      </c>
+      <c r="AA18">
+        <v>16</v>
+      </c>
       <c r="AB18" s="1">
         <v>0</v>
       </c>
@@ -2371,6 +2452,9 @@
       <c r="A19" t="s">
         <v>85</v>
       </c>
+      <c r="AA19">
+        <v>2</v>
+      </c>
       <c r="AB19" s="1">
         <v>0</v>
       </c>
@@ -2409,6 +2493,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="AA20">
+        <v>11</v>
+      </c>
       <c r="AB20">
         <v>3</v>
       </c>
@@ -2447,6 +2534,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="AA21">
+        <v>10</v>
+      </c>
       <c r="AB21">
         <v>17</v>
       </c>
@@ -2485,6 +2575,12 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="Z22">
+        <v>15</v>
+      </c>
+      <c r="AA22">
+        <v>11</v>
+      </c>
       <c r="AB22">
         <v>15</v>
       </c>
@@ -2523,6 +2619,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AA23">
+        <v>17</v>
+      </c>
       <c r="AB23">
         <v>0</v>
       </c>
@@ -2561,6 +2660,9 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
+      <c r="AA24">
+        <v>16</v>
+      </c>
       <c r="AB24" s="1">
         <v>0</v>
       </c>
@@ -2599,6 +2701,12 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
+      <c r="Z25">
+        <v>16</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
       <c r="AB25">
         <v>16</v>
       </c>
@@ -2637,7 +2745,9 @@
       <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="AA26" s="1"/>
+      <c r="AA26" s="1">
+        <v>0</v>
+      </c>
       <c r="AB26" s="1">
         <v>0</v>
       </c>
@@ -2676,7 +2786,9 @@
       <c r="A27" t="s">
         <v>46</v>
       </c>
-      <c r="AA27" s="1"/>
+      <c r="AA27" s="1">
+        <v>0</v>
+      </c>
       <c r="AB27" s="1">
         <v>0</v>
       </c>
@@ -2715,6 +2827,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
       <c r="AB28">
         <v>17</v>
       </c>
@@ -2753,7 +2868,9 @@
       <c r="A29" t="s">
         <v>48</v>
       </c>
-      <c r="AA29" s="1"/>
+      <c r="AA29" s="1">
+        <v>0</v>
+      </c>
       <c r="AB29" s="1">
         <v>0</v>
       </c>
@@ -2792,7 +2909,12 @@
       <c r="A30" t="s">
         <v>49</v>
       </c>
-      <c r="AA30" s="1"/>
+      <c r="Z30">
+        <v>16</v>
+      </c>
+      <c r="AA30" s="1">
+        <v>0</v>
+      </c>
       <c r="AB30" s="1">
         <v>0</v>
       </c>
@@ -2831,6 +2953,9 @@
       <c r="A31" t="s">
         <v>53</v>
       </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
       <c r="AB31">
         <v>0</v>
       </c>
@@ -2869,7 +2994,9 @@
       <c r="A32" t="s">
         <v>57</v>
       </c>
-      <c r="AA32" s="1"/>
+      <c r="AA32" s="1">
+        <v>0</v>
+      </c>
       <c r="AB32" s="1">
         <v>0</v>
       </c>
@@ -2908,7 +3035,9 @@
       <c r="A33" t="s">
         <v>58</v>
       </c>
-      <c r="AA33" s="1"/>
+      <c r="AA33" s="1">
+        <v>0</v>
+      </c>
       <c r="AB33" s="1">
         <v>0</v>
       </c>
@@ -2947,7 +3076,9 @@
       <c r="A34" t="s">
         <v>59</v>
       </c>
-      <c r="AA34" s="1"/>
+      <c r="AA34" s="1">
+        <v>0</v>
+      </c>
       <c r="AB34" s="1">
         <v>0</v>
       </c>
@@ -2986,7 +3117,9 @@
       <c r="A35" t="s">
         <v>60</v>
       </c>
-      <c r="AA35" s="1"/>
+      <c r="AA35" s="1">
+        <v>0</v>
+      </c>
       <c r="AB35" s="1">
         <v>0</v>
       </c>
@@ -3025,7 +3158,9 @@
       <c r="A36" t="s">
         <v>61</v>
       </c>
-      <c r="AA36" s="1"/>
+      <c r="AA36" s="1">
+        <v>0</v>
+      </c>
       <c r="AB36" s="1">
         <v>0</v>
       </c>
@@ -3065,7 +3200,9 @@
         <v>62</v>
       </c>
       <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
+      <c r="AA37" s="1">
+        <v>0</v>
+      </c>
       <c r="AB37" s="1">
         <v>0</v>
       </c>
@@ -3105,7 +3242,9 @@
         <v>63</v>
       </c>
       <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
       <c r="AB38" s="1">
         <v>0</v>
       </c>
@@ -3144,6 +3283,9 @@
       <c r="A39" t="s">
         <v>64</v>
       </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
       <c r="AB39">
         <v>2</v>
       </c>
@@ -3183,7 +3325,9 @@
         <v>65</v>
       </c>
       <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
+      <c r="AA40" s="1">
+        <v>0</v>
+      </c>
       <c r="AB40" s="1">
         <v>0</v>
       </c>
@@ -3223,7 +3367,9 @@
         <v>66</v>
       </c>
       <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
+      <c r="AA41" s="1">
+        <v>0</v>
+      </c>
       <c r="AB41" s="1">
         <v>0</v>
       </c>
@@ -3264,7 +3410,9 @@
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
+      <c r="AA42" s="1">
+        <v>0</v>
+      </c>
       <c r="AB42" s="1">
         <v>0</v>
       </c>
@@ -3303,6 +3451,9 @@
       <c r="A43" t="s">
         <v>68</v>
       </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
       <c r="AB43">
         <v>0</v>
       </c>
@@ -3343,7 +3494,9 @@
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
+      <c r="AA44" s="1">
+        <v>0</v>
+      </c>
       <c r="AB44" s="1">
         <v>0</v>
       </c>
@@ -3384,7 +3537,9 @@
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
+      <c r="AA45" s="1">
+        <v>0</v>
+      </c>
       <c r="AB45" s="1">
         <v>0</v>
       </c>
@@ -3425,7 +3580,9 @@
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
+      <c r="AA46" s="1">
+        <v>0</v>
+      </c>
       <c r="AB46" s="1">
         <v>0</v>
       </c>
@@ -3466,7 +3623,9 @@
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
+      <c r="AA47" s="1">
+        <v>0</v>
+      </c>
       <c r="AB47" s="1">
         <v>0</v>
       </c>
@@ -3507,7 +3666,9 @@
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
+      <c r="AA48" s="1">
+        <v>0</v>
+      </c>
       <c r="AB48" s="1">
         <v>0</v>
       </c>
@@ -3549,7 +3710,9 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
+      <c r="AA49" s="1">
+        <v>0</v>
+      </c>
       <c r="AB49" s="1">
         <v>0</v>
       </c>
@@ -3591,7 +3754,9 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
+      <c r="AA50" s="1">
+        <v>0</v>
+      </c>
       <c r="AB50" s="1">
         <v>0</v>
       </c>
@@ -3633,7 +3798,9 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
+      <c r="AA51" s="1">
+        <v>0</v>
+      </c>
       <c r="AB51" s="1">
         <v>0</v>
       </c>
@@ -3675,7 +3842,9 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
+      <c r="AA52" s="1">
+        <v>0</v>
+      </c>
       <c r="AB52" s="1">
         <v>0</v>
       </c>
@@ -3717,7 +3886,9 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
-      <c r="AA53" s="1"/>
+      <c r="AA53" s="1">
+        <v>0</v>
+      </c>
       <c r="AB53" s="1">
         <v>0</v>
       </c>
@@ -3759,7 +3930,9 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
+      <c r="AA54" s="1">
+        <v>0</v>
+      </c>
       <c r="AB54" s="1">
         <v>0</v>
       </c>
@@ -3802,7 +3975,9 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="1"/>
+      <c r="AA55" s="1">
+        <v>0</v>
+      </c>
       <c r="AB55" s="1">
         <v>0</v>
       </c>
@@ -3845,7 +4020,9 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
+      <c r="AA56" s="1">
+        <v>0</v>
+      </c>
       <c r="AB56" s="1">
         <v>0</v>
       </c>
@@ -3888,7 +4065,9 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
+      <c r="AA57" s="1">
+        <v>0</v>
+      </c>
       <c r="AB57" s="1">
         <v>0</v>
       </c>
@@ -3931,7 +4110,9 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
+      <c r="AA58" s="1">
+        <v>0</v>
+      </c>
       <c r="AB58" s="1">
         <v>0</v>
       </c>
@@ -3974,7 +4155,9 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
-      <c r="AA59" s="1"/>
+      <c r="AA59" s="1">
+        <v>0</v>
+      </c>
       <c r="AB59" s="1">
         <v>0</v>
       </c>
@@ -4018,7 +4201,9 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
-      <c r="AA60" s="1"/>
+      <c r="AA60" s="1">
+        <v>0</v>
+      </c>
       <c r="AB60" s="1">
         <v>0</v>
       </c>
@@ -4062,7 +4247,9 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
-      <c r="AA61" s="1"/>
+      <c r="AA61" s="1">
+        <v>0</v>
+      </c>
       <c r="AB61" s="1">
         <v>0</v>
       </c>
@@ -4107,7 +4294,9 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
-      <c r="AA62" s="1"/>
+      <c r="AA62" s="1">
+        <v>0</v>
+      </c>
       <c r="AB62" s="1">
         <v>0</v>
       </c>
@@ -4152,7 +4341,9 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
-      <c r="AA63" s="1"/>
+      <c r="AA63" s="1">
+        <v>0</v>
+      </c>
       <c r="AB63" s="1">
         <v>0</v>
       </c>
@@ -4197,7 +4388,9 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
-      <c r="AA64" s="1"/>
+      <c r="AA64" s="1">
+        <v>0</v>
+      </c>
       <c r="AB64" s="1">
         <v>0</v>
       </c>
@@ -4242,7 +4435,9 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
-      <c r="AA65" s="1"/>
+      <c r="AA65" s="1">
+        <v>0</v>
+      </c>
       <c r="AB65" s="1">
         <v>0</v>
       </c>
@@ -4347,7 +4542,9 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
-      <c r="AA67" s="1"/>
+      <c r="AA67" s="1">
+        <v>0</v>
+      </c>
       <c r="AB67" s="1">
         <v>0</v>
       </c>
@@ -4393,7 +4590,9 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
-      <c r="AA68" s="1"/>
+      <c r="AA68" s="1">
+        <v>0</v>
+      </c>
       <c r="AB68" s="1">
         <v>0</v>
       </c>
@@ -4439,7 +4638,9 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
-      <c r="AA69" s="1"/>
+      <c r="AA69" s="1">
+        <v>0</v>
+      </c>
       <c r="AB69" s="1">
         <v>0</v>
       </c>
@@ -4485,7 +4686,9 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
-      <c r="AA70" s="1"/>
+      <c r="AA70" s="1">
+        <v>0</v>
+      </c>
       <c r="AB70" s="1">
         <v>0</v>
       </c>
@@ -4531,7 +4734,9 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
-      <c r="AA71" s="1"/>
+      <c r="AA71" s="1">
+        <v>0</v>
+      </c>
       <c r="AB71" s="1">
         <v>0</v>
       </c>
@@ -4578,7 +4783,9 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
-      <c r="AA72" s="1"/>
+      <c r="AA72" s="1">
+        <v>0</v>
+      </c>
       <c r="AB72" s="1">
         <v>0</v>
       </c>
@@ -4625,7 +4832,9 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
-      <c r="AA73" s="1"/>
+      <c r="AA73" s="1">
+        <v>0</v>
+      </c>
       <c r="AB73" s="1">
         <v>0</v>
       </c>
@@ -4672,7 +4881,9 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
-      <c r="AA74" s="1"/>
+      <c r="AA74" s="1">
+        <v>0</v>
+      </c>
       <c r="AB74" s="1">
         <v>0</v>
       </c>
@@ -4719,7 +4930,9 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
-      <c r="AA75" s="1"/>
+      <c r="AA75" s="1">
+        <v>0</v>
+      </c>
       <c r="AB75" s="1">
         <v>0</v>
       </c>
@@ -4766,7 +4979,9 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
-      <c r="AA76" s="1"/>
+      <c r="AA76" s="1">
+        <v>0</v>
+      </c>
       <c r="AB76" s="1">
         <v>0</v>
       </c>
@@ -4814,7 +5029,9 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
-      <c r="AA77" s="1"/>
+      <c r="AA77" s="1">
+        <v>0</v>
+      </c>
       <c r="AB77" s="1">
         <v>0</v>
       </c>
@@ -4862,7 +5079,9 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
-      <c r="AA78" s="1"/>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
       <c r="AB78" s="1">
         <v>0</v>
       </c>
@@ -4911,7 +5130,9 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
-      <c r="AA79" s="1"/>
+      <c r="AA79" s="1">
+        <v>0</v>
+      </c>
       <c r="AB79" s="1">
         <v>0</v>
       </c>
@@ -4960,7 +5181,9 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
-      <c r="AA80" s="1"/>
+      <c r="AA80" s="1">
+        <v>0</v>
+      </c>
       <c r="AB80" s="1">
         <v>0</v>
       </c>
@@ -5009,7 +5232,9 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
-      <c r="AA81" s="1"/>
+      <c r="AA81" s="1">
+        <v>0</v>
+      </c>
       <c r="AB81" s="1">
         <v>0</v>
       </c>
@@ -5058,7 +5283,9 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
-      <c r="AA82" s="1"/>
+      <c r="AA82" s="1">
+        <v>0</v>
+      </c>
       <c r="AB82" s="1">
         <v>0</v>
       </c>
@@ -5107,7 +5334,9 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
-      <c r="AA83" s="1"/>
+      <c r="AA83" s="1">
+        <v>0</v>
+      </c>
       <c r="AB83" s="1">
         <v>0</v>
       </c>
@@ -5157,7 +5386,9 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
-      <c r="AA84" s="1"/>
+      <c r="AA84" s="1">
+        <v>0</v>
+      </c>
       <c r="AB84" s="1">
         <v>0</v>
       </c>
@@ -5207,7 +5438,9 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
-      <c r="AA85" s="1"/>
+      <c r="AA85" s="1">
+        <v>0</v>
+      </c>
       <c r="AB85" s="1">
         <v>0</v>
       </c>
@@ -5257,7 +5490,9 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
-      <c r="AA86" s="1"/>
+      <c r="AA86" s="1">
+        <v>0</v>
+      </c>
       <c r="AB86" s="1">
         <v>0</v>
       </c>
@@ -5307,7 +5542,9 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
-      <c r="AA87" s="1"/>
+      <c r="AA87" s="1">
+        <v>0</v>
+      </c>
       <c r="AB87" s="1">
         <v>0</v>
       </c>
@@ -5358,7 +5595,9 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
-      <c r="AA88" s="1"/>
+      <c r="AA88" s="1">
+        <v>0</v>
+      </c>
       <c r="AB88" s="1">
         <v>0</v>
       </c>
@@ -5409,7 +5648,9 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
-      <c r="AA89" s="1"/>
+      <c r="AA89" s="1">
+        <v>0</v>
+      </c>
       <c r="AB89" s="1">
         <v>0</v>
       </c>
@@ -5460,7 +5701,9 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
-      <c r="AA90" s="1"/>
+      <c r="AA90" s="1">
+        <v>0</v>
+      </c>
       <c r="AB90" s="1">
         <v>0</v>
       </c>
@@ -5511,7 +5754,9 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
-      <c r="AA91" s="1"/>
+      <c r="AA91" s="1">
+        <v>0</v>
+      </c>
       <c r="AB91" s="1">
         <v>0</v>
       </c>
@@ -5562,7 +5807,9 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
-      <c r="AA92" s="1"/>
+      <c r="AA92" s="1">
+        <v>0</v>
+      </c>
       <c r="AB92" s="1">
         <v>0</v>
       </c>
@@ -5614,7 +5861,9 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
-      <c r="AA93" s="1"/>
+      <c r="AA93" s="1">
+        <v>0</v>
+      </c>
       <c r="AB93" s="1">
         <v>0</v>
       </c>
@@ -5666,7 +5915,9 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
-      <c r="AA94" s="1"/>
+      <c r="AA94" s="1">
+        <v>0</v>
+      </c>
       <c r="AB94" s="1">
         <v>0</v>
       </c>
@@ -5718,7 +5969,9 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
-      <c r="AA95" s="1"/>
+      <c r="AA95" s="1">
+        <v>0</v>
+      </c>
       <c r="AB95" s="1">
         <v>0</v>
       </c>
@@ -5770,7 +6023,9 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
-      <c r="AA96" s="1"/>
+      <c r="AA96" s="1">
+        <v>0</v>
+      </c>
       <c r="AB96" s="1">
         <v>0</v>
       </c>
@@ -5822,7 +6077,9 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
-      <c r="AA97" s="1"/>
+      <c r="AA97" s="1">
+        <v>0</v>
+      </c>
       <c r="AB97" s="1">
         <v>0</v>
       </c>
@@ -5875,7 +6132,9 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
-      <c r="AA98" s="1"/>
+      <c r="AA98" s="1">
+        <v>0</v>
+      </c>
       <c r="AB98" s="1">
         <v>0</v>
       </c>
@@ -5928,7 +6187,9 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
-      <c r="AA99" s="1"/>
+      <c r="AA99" s="1">
+        <v>0</v>
+      </c>
       <c r="AB99" s="1">
         <v>0</v>
       </c>
@@ -5981,7 +6242,9 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
-      <c r="AA100" s="1"/>
+      <c r="AA100" s="1">
+        <v>0</v>
+      </c>
       <c r="AB100" s="1">
         <v>0</v>
       </c>
@@ -6034,7 +6297,9 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
-      <c r="AA101" s="1"/>
+      <c r="AA101" s="1">
+        <v>0</v>
+      </c>
       <c r="AB101" s="1">
         <v>0</v>
       </c>
@@ -6088,7 +6353,9 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
-      <c r="AA102" s="1"/>
+      <c r="AA102" s="1">
+        <v>0</v>
+      </c>
       <c r="AB102" s="1">
         <v>0</v>
       </c>
@@ -6142,7 +6409,9 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
-      <c r="AA103" s="1"/>
+      <c r="AA103" s="1">
+        <v>0</v>
+      </c>
       <c r="AB103" s="1">
         <v>0</v>
       </c>
@@ -6197,7 +6466,9 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
-      <c r="AA104" s="1"/>
+      <c r="AA104" s="1">
+        <v>0</v>
+      </c>
       <c r="AB104" s="1">
         <v>0</v>
       </c>
@@ -6252,7 +6523,9 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
-      <c r="AA105" s="1"/>
+      <c r="AA105" s="1">
+        <v>0</v>
+      </c>
       <c r="AB105" s="1">
         <v>0</v>
       </c>
@@ -6307,7 +6580,9 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
-      <c r="AA106" s="1"/>
+      <c r="AA106" s="1">
+        <v>0</v>
+      </c>
       <c r="AB106" s="1">
         <v>0</v>
       </c>
@@ -6363,7 +6638,9 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
-      <c r="AA107" s="1"/>
+      <c r="AA107" s="1">
+        <v>0</v>
+      </c>
       <c r="AB107" s="1">
         <v>0</v>
       </c>
@@ -6419,7 +6696,9 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
-      <c r="AA108" s="1"/>
+      <c r="AA108" s="1">
+        <v>0</v>
+      </c>
       <c r="AB108" s="1">
         <v>0</v>
       </c>
@@ -6475,7 +6754,9 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
-      <c r="AA109" s="1"/>
+      <c r="AA109" s="1">
+        <v>0</v>
+      </c>
       <c r="AB109" s="1">
         <v>0</v>
       </c>
@@ -6532,7 +6813,9 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
-      <c r="AA110" s="1"/>
+      <c r="AA110" s="1">
+        <v>0</v>
+      </c>
       <c r="AB110" s="1">
         <v>0</v>
       </c>
@@ -6589,7 +6872,9 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
-      <c r="AA111" s="1"/>
+      <c r="AA111" s="1">
+        <v>0</v>
+      </c>
       <c r="AB111" s="1">
         <v>0</v>
       </c>
@@ -6646,7 +6931,9 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
-      <c r="AA112" s="1"/>
+      <c r="AA112" s="1">
+        <v>0</v>
+      </c>
       <c r="AB112" s="1">
         <v>0</v>
       </c>
@@ -6704,7 +6991,9 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
-      <c r="AA113" s="1"/>
+      <c r="AA113" s="1">
+        <v>0</v>
+      </c>
       <c r="AB113" s="1">
         <v>0</v>
       </c>
@@ -6762,7 +7051,9 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
-      <c r="AA114" s="1"/>
+      <c r="AA114" s="1">
+        <v>0</v>
+      </c>
       <c r="AB114" s="1">
         <v>0</v>
       </c>
@@ -6821,7 +7112,9 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
-      <c r="AA115" s="1"/>
+      <c r="AA115" s="1">
+        <v>0</v>
+      </c>
       <c r="AB115" s="1">
         <v>0</v>
       </c>
@@ -6880,7 +7173,9 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
-      <c r="AA116" s="1"/>
+      <c r="AA116" s="1">
+        <v>0</v>
+      </c>
       <c r="AB116" s="1">
         <v>0</v>
       </c>
@@ -6939,7 +7234,9 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
-      <c r="AA117" s="1"/>
+      <c r="AA117" s="1">
+        <v>0</v>
+      </c>
       <c r="AB117" s="1">
         <v>0</v>
       </c>
@@ -6999,7 +7296,9 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
-      <c r="AA118" s="1"/>
+      <c r="AA118" s="1">
+        <v>0</v>
+      </c>
       <c r="AB118" s="1">
         <v>0</v>
       </c>
@@ -7059,7 +7358,9 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
-      <c r="AA119" s="1"/>
+      <c r="AA119" s="1">
+        <v>0</v>
+      </c>
       <c r="AB119" s="1">
         <v>0</v>
       </c>
@@ -7119,7 +7420,9 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
-      <c r="AA120" s="1"/>
+      <c r="AA120" s="1">
+        <v>0</v>
+      </c>
       <c r="AB120" s="1">
         <v>0</v>
       </c>
@@ -7180,7 +7483,9 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
-      <c r="AA121" s="1"/>
+      <c r="AA121" s="1">
+        <v>0</v>
+      </c>
       <c r="AB121" s="1">
         <v>0</v>
       </c>
@@ -7241,7 +7546,9 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
-      <c r="AA122" s="1"/>
+      <c r="AA122" s="1">
+        <v>0</v>
+      </c>
       <c r="AB122" s="1">
         <v>0</v>
       </c>
@@ -7302,7 +7609,9 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
-      <c r="AA123" s="1"/>
+      <c r="AA123" s="1">
+        <v>0</v>
+      </c>
       <c r="AB123" s="1">
         <v>0</v>
       </c>
@@ -7364,7 +7673,9 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
-      <c r="AA124" s="1"/>
+      <c r="AA124" s="1">
+        <v>0</v>
+      </c>
       <c r="AB124" s="1">
         <v>0</v>
       </c>
@@ -10804,9 +11115,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -10874,7 +11198,58 @@
       </c>
       <c r="B2">
         <f>SUM(C2:C2:S2)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -10883,7 +11258,58 @@
       </c>
       <c r="B3">
         <f>SUM(C3:C3:S3)</f>
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -10892,7 +11318,58 @@
       </c>
       <c r="B4">
         <f>SUM(C4:C4:S4)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -10901,7 +11378,58 @@
       </c>
       <c r="B5">
         <f>SUM(C5:C5:S5)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -10910,7 +11438,58 @@
       </c>
       <c r="B6">
         <f>SUM(C6:C6:S6)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -10919,7 +11498,58 @@
       </c>
       <c r="B7">
         <f>SUM(C7:C7:S7)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -10928,7 +11558,58 @@
       </c>
       <c r="B8">
         <f>SUM(C8:C8:S8)</f>
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -10937,7 +11618,58 @@
       </c>
       <c r="B9">
         <f>SUM(C9:C9:S9)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -10946,7 +11678,58 @@
       </c>
       <c r="B10">
         <f>SUM(C10:C10:S10)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -10955,7 +11738,58 @@
       </c>
       <c r="B11">
         <f>SUM(C11:C11:S11)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -10964,7 +11798,58 @@
       </c>
       <c r="B12">
         <f>SUM(C12:C12:S12)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -10973,7 +11858,58 @@
       </c>
       <c r="B13">
         <f>SUM(C13:C13:S13)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -10982,7 +11918,58 @@
       </c>
       <c r="B14">
         <f>SUM(C14:C14:S14)</f>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -10991,7 +11978,58 @@
       </c>
       <c r="B15">
         <f>SUM(C15:C15:S15)</f>
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -11000,78 +12038,537 @@
       </c>
       <c r="B16">
         <f>SUM(C16:C16:S16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
         <f>SUM(C17:C17:S17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
         <f>SUM(C18:C18:S18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19">
         <f>SUM(C19:C19:S19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20">
         <f>SUM(C20:C20:S20)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21">
         <f>SUM(C21:C21:S21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22">
         <f>SUM(C22:C22:S22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23">
         <f>SUM(C23:C23:S23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24">
         <f>SUM(C24:C24:S24)</f>
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
         <v>0</v>
       </c>
     </row>
@@ -11082,139 +12579,1450 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <f t="shared" ref="B3:B25" si="0">SUM(C3:R3)</f>
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB09F56D-2401-4DF1-8D83-BC50326EE30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32D8CF9-DE86-42D7-B5CA-227A7829E748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="6" activeTab="13" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="75" yWindow="60" windowWidth="16410" windowHeight="15480" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="150">
   <si>
     <t>Driver</t>
   </si>
@@ -206,16 +206,7 @@
     <t>Fernando Alonso</t>
   </si>
   <si>
-    <t>Ralph Firman</t>
-  </si>
-  <si>
-    <t>Antônio Pizzonia</t>
-  </si>
-  <si>
     <t>Jos Verstappen</t>
-  </si>
-  <si>
-    <t>Justin Wilson</t>
   </si>
   <si>
     <t>Cristiano da Matta</t>
@@ -1084,13 +1075,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1133,13 +1124,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1601,10 +1592,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AL124"/>
+  <dimension ref="A1:AL121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1989,6 +1980,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
       <c r="AA8">
         <v>16</v>
       </c>
@@ -2030,6 +2024,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="Z9">
+        <v>16</v>
+      </c>
       <c r="AA9">
         <v>17</v>
       </c>
@@ -2071,6 +2068,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="Z10">
+        <v>14</v>
+      </c>
       <c r="AA10">
         <v>17</v>
       </c>
@@ -2112,6 +2112,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="Z11">
+        <v>16</v>
+      </c>
       <c r="AA11">
         <v>17</v>
       </c>
@@ -2241,6 +2244,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="Z14">
+        <v>1</v>
+      </c>
       <c r="AA14">
         <v>17</v>
       </c>
@@ -2326,6 +2332,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
       <c r="AA16">
         <v>17</v>
       </c>
@@ -2367,6 +2376,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
       <c r="AA17">
         <v>17</v>
       </c>
@@ -2450,7 +2462,10 @@
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>82</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
       </c>
       <c r="AA19">
         <v>2</v>
@@ -2493,6 +2508,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
       <c r="AA20">
         <v>11</v>
       </c>
@@ -2534,6 +2552,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
       <c r="AA21">
         <v>10</v>
       </c>
@@ -2573,7 +2594,7 @@
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Z22">
         <v>15</v>
@@ -2619,6 +2640,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
       <c r="AA23">
         <v>17</v>
       </c>
@@ -2660,6 +2684,9 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
       <c r="AA24">
         <v>16</v>
       </c>
@@ -2745,32 +2772,35 @@
       <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="AA26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="1">
-        <v>0</v>
+      <c r="Z26">
+        <v>16</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>17</v>
+      </c>
+      <c r="AC26">
+        <v>17</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
       </c>
-      <c r="AE26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="1">
-        <v>0</v>
+      <c r="AE26">
+        <v>9</v>
+      </c>
+      <c r="AF26">
+        <v>17</v>
+      </c>
+      <c r="AG26">
+        <v>16</v>
+      </c>
+      <c r="AH26">
+        <v>5</v>
+      </c>
+      <c r="AI26">
+        <v>10</v>
       </c>
       <c r="AJ26" s="1">
         <v>0</v>
@@ -2786,6 +2816,9 @@
       <c r="A27" t="s">
         <v>46</v>
       </c>
+      <c r="Z27">
+        <v>16</v>
+      </c>
       <c r="AA27" s="1">
         <v>0</v>
       </c>
@@ -2825,34 +2858,37 @@
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="Z28">
+        <v>1</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC28">
         <v>17</v>
       </c>
-      <c r="AD28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>9</v>
-      </c>
-      <c r="AF28">
-        <v>17</v>
-      </c>
-      <c r="AG28">
+      <c r="AD28">
         <v>16</v>
       </c>
-      <c r="AH28">
-        <v>5</v>
-      </c>
-      <c r="AI28">
-        <v>10</v>
+      <c r="AE28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="1">
+        <v>0</v>
       </c>
       <c r="AJ28" s="1">
         <v>0</v>
@@ -2866,7 +2902,10 @@
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>54</v>
+      </c>
+      <c r="Z29">
+        <v>14</v>
       </c>
       <c r="AA29" s="1">
         <v>0</v>
@@ -2907,7 +2946,7 @@
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Z30">
         <v>16</v>
@@ -2951,19 +2990,22 @@
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>17</v>
-      </c>
-      <c r="AD31">
-        <v>16</v>
+        <v>56</v>
+      </c>
+      <c r="Z31">
+        <v>11</v>
+      </c>
+      <c r="AA31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="1">
+        <v>0</v>
       </c>
       <c r="AE31" s="1">
         <v>0</v>
@@ -2994,6 +3036,9 @@
       <c r="A32" t="s">
         <v>57</v>
       </c>
+      <c r="Z32">
+        <v>5</v>
+      </c>
       <c r="AA32" s="1">
         <v>0</v>
       </c>
@@ -3035,6 +3080,9 @@
       <c r="A33" t="s">
         <v>58</v>
       </c>
+      <c r="Z33">
+        <v>2</v>
+      </c>
       <c r="AA33" s="1">
         <v>0</v>
       </c>
@@ -3076,6 +3124,9 @@
       <c r="A34" t="s">
         <v>59</v>
       </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
       <c r="AA34" s="1">
         <v>0</v>
       </c>
@@ -3117,6 +3168,9 @@
       <c r="A35" t="s">
         <v>60</v>
       </c>
+      <c r="Z35" s="1">
+        <v>0</v>
+      </c>
       <c r="AA35" s="1">
         <v>0</v>
       </c>
@@ -3158,17 +3212,20 @@
       <c r="A36" t="s">
         <v>61</v>
       </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="1">
-        <v>0</v>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>2</v>
+      </c>
+      <c r="AC36">
+        <v>17</v>
+      </c>
+      <c r="AD36">
+        <v>12</v>
       </c>
       <c r="AE36" s="1">
         <v>0</v>
@@ -3199,7 +3256,9 @@
       <c r="A37" t="s">
         <v>62</v>
       </c>
-      <c r="Z37" s="1"/>
+      <c r="Z37" s="1">
+        <v>0</v>
+      </c>
       <c r="AA37" s="1">
         <v>0</v>
       </c>
@@ -3241,7 +3300,9 @@
       <c r="A38" t="s">
         <v>63</v>
       </c>
-      <c r="Z38" s="1"/>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
       <c r="AA38" s="1">
         <v>0</v>
       </c>
@@ -3283,17 +3344,21 @@
       <c r="A39" t="s">
         <v>64</v>
       </c>
-      <c r="AA39">
-        <v>0</v>
-      </c>
-      <c r="AB39">
-        <v>2</v>
-      </c>
-      <c r="AC39">
-        <v>17</v>
-      </c>
-      <c r="AD39">
-        <v>12</v>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="1">
+        <v>0</v>
       </c>
       <c r="AE39" s="1">
         <v>0</v>
@@ -3324,24 +3389,26 @@
       <c r="A40" t="s">
         <v>65</v>
       </c>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="1">
-        <v>0</v>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>17</v>
+      </c>
+      <c r="AD40">
+        <v>16</v>
+      </c>
+      <c r="AE40">
+        <v>16</v>
+      </c>
+      <c r="AF40">
+        <v>3</v>
       </c>
       <c r="AG40" s="1">
         <v>0</v>
@@ -3366,7 +3433,10 @@
       <c r="A41" t="s">
         <v>66</v>
       </c>
-      <c r="Z41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
       <c r="AA41" s="1">
         <v>0</v>
       </c>
@@ -3409,7 +3479,9 @@
         <v>67</v>
       </c>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
+      <c r="Z42" s="1">
+        <v>0</v>
+      </c>
       <c r="AA42" s="1">
         <v>0</v>
       </c>
@@ -3451,23 +3523,27 @@
       <c r="A43" t="s">
         <v>68</v>
       </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>17</v>
-      </c>
-      <c r="AD43">
-        <v>16</v>
-      </c>
-      <c r="AE43">
-        <v>16</v>
-      </c>
-      <c r="AF43">
-        <v>3</v>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="1">
+        <v>0</v>
       </c>
       <c r="AG43" s="1">
         <v>0</v>
@@ -3493,7 +3569,9 @@
         <v>69</v>
       </c>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
+      <c r="Z44" s="1">
+        <v>0</v>
+      </c>
       <c r="AA44" s="1">
         <v>0</v>
       </c>
@@ -3536,7 +3614,9 @@
         <v>70</v>
       </c>
       <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
       <c r="AA45" s="1">
         <v>0</v>
       </c>
@@ -3578,8 +3658,11 @@
       <c r="A46" t="s">
         <v>71</v>
       </c>
+      <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
+      <c r="Z46" s="1">
+        <v>0</v>
+      </c>
       <c r="AA46" s="1">
         <v>0</v>
       </c>
@@ -3621,8 +3704,11 @@
       <c r="A47" t="s">
         <v>72</v>
       </c>
+      <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
+      <c r="Z47" s="1">
+        <v>0</v>
+      </c>
       <c r="AA47" s="1">
         <v>0</v>
       </c>
@@ -3664,8 +3750,11 @@
       <c r="A48" t="s">
         <v>73</v>
       </c>
+      <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
+      <c r="Z48" s="1">
+        <v>0</v>
+      </c>
       <c r="AA48" s="1">
         <v>0</v>
       </c>
@@ -3709,7 +3798,9 @@
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
+      <c r="Z49" s="1">
+        <v>0</v>
+      </c>
       <c r="AA49" s="1">
         <v>0</v>
       </c>
@@ -3753,7 +3844,9 @@
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
+      <c r="Z50" s="1">
+        <v>0</v>
+      </c>
       <c r="AA50" s="1">
         <v>0</v>
       </c>
@@ -3797,7 +3890,9 @@
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
+      <c r="Z51" s="1">
+        <v>0</v>
+      </c>
       <c r="AA51" s="1">
         <v>0</v>
       </c>
@@ -3839,9 +3934,12 @@
       <c r="A52" t="s">
         <v>77</v>
       </c>
+      <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
+      <c r="Z52" s="1">
+        <v>0</v>
+      </c>
       <c r="AA52" s="1">
         <v>0</v>
       </c>
@@ -3883,9 +3981,12 @@
       <c r="A53" t="s">
         <v>78</v>
       </c>
+      <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
+      <c r="Z53" s="1">
+        <v>0</v>
+      </c>
       <c r="AA53" s="1">
         <v>0</v>
       </c>
@@ -3927,9 +4028,12 @@
       <c r="A54" t="s">
         <v>79</v>
       </c>
+      <c r="W54" s="1"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
+      <c r="Z54" s="1">
+        <v>0</v>
+      </c>
       <c r="AA54" s="1">
         <v>0</v>
       </c>
@@ -3974,7 +4078,9 @@
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
+      <c r="Z55" s="1">
+        <v>0</v>
+      </c>
       <c r="AA55" s="1">
         <v>0</v>
       </c>
@@ -4019,7 +4125,9 @@
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
+      <c r="Z56" s="1">
+        <v>0</v>
+      </c>
       <c r="AA56" s="1">
         <v>0</v>
       </c>
@@ -4059,12 +4167,15 @@
     </row>
     <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>82</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
       <c r="AA57" s="1">
         <v>0</v>
       </c>
@@ -4104,12 +4215,15 @@
     </row>
     <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>83</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="V58" s="1"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
+      <c r="Z58" s="1">
+        <v>0</v>
+      </c>
       <c r="AA58" s="1">
         <v>0</v>
       </c>
@@ -4149,12 +4263,16 @@
     </row>
     <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>84</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
+      <c r="Z59" s="1">
+        <v>0</v>
+      </c>
       <c r="AA59" s="1">
         <v>0</v>
       </c>
@@ -4196,11 +4314,14 @@
       <c r="A60" t="s">
         <v>86</v>
       </c>
+      <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
-      <c r="Z60" s="1"/>
+      <c r="Z60" s="1">
+        <v>0</v>
+      </c>
       <c r="AA60" s="1">
         <v>0</v>
       </c>
@@ -4242,11 +4363,14 @@
       <c r="A61" t="s">
         <v>87</v>
       </c>
+      <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
-      <c r="Z61" s="1"/>
+      <c r="Z61" s="1">
+        <v>0</v>
+      </c>
       <c r="AA61" s="1">
         <v>0</v>
       </c>
@@ -4293,7 +4417,9 @@
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
+      <c r="Z62" s="1">
+        <v>0</v>
+      </c>
       <c r="AA62" s="1">
         <v>0</v>
       </c>
@@ -4335,12 +4461,24 @@
       <c r="A63" t="s">
         <v>89</v>
       </c>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
-      <c r="Z63" s="1"/>
+      <c r="U63" s="1">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="1">
+        <v>0</v>
+      </c>
       <c r="AA63" s="1">
         <v>0</v>
       </c>
@@ -4350,8 +4488,8 @@
       <c r="AC63" s="1">
         <v>0</v>
       </c>
-      <c r="AD63" s="1">
-        <v>0</v>
+      <c r="AD63">
+        <v>15</v>
       </c>
       <c r="AE63" s="1">
         <v>0</v>
@@ -4359,17 +4497,17 @@
       <c r="AF63" s="1">
         <v>0</v>
       </c>
-      <c r="AG63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH63" s="1">
-        <v>0</v>
+      <c r="AG63">
+        <v>6</v>
+      </c>
+      <c r="AH63">
+        <v>15</v>
       </c>
       <c r="AI63" s="1">
         <v>0</v>
       </c>
-      <c r="AJ63" s="1">
-        <v>0</v>
+      <c r="AJ63">
+        <v>12</v>
       </c>
       <c r="AK63" s="1">
         <v>0</v>
@@ -4382,12 +4520,15 @@
       <c r="A64" t="s">
         <v>90</v>
       </c>
+      <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
+      <c r="Z64" s="1">
+        <v>0</v>
+      </c>
       <c r="AA64" s="1">
         <v>0</v>
       </c>
@@ -4429,12 +4570,15 @@
       <c r="A65" t="s">
         <v>91</v>
       </c>
+      <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
+      <c r="Z65" s="1">
+        <v>0</v>
+      </c>
       <c r="AA65" s="1">
         <v>0</v>
       </c>
@@ -4476,21 +4620,12 @@
       <c r="A66" t="s">
         <v>92</v>
       </c>
-      <c r="U66" s="1">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1">
-        <v>0</v>
-      </c>
-      <c r="W66" s="1">
-        <v>0</v>
-      </c>
-      <c r="X66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="1">
-        <v>0</v>
-      </c>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
       <c r="Z66" s="1">
         <v>0</v>
       </c>
@@ -4503,8 +4638,8 @@
       <c r="AC66" s="1">
         <v>0</v>
       </c>
-      <c r="AD66">
-        <v>15</v>
+      <c r="AD66" s="1">
+        <v>0</v>
       </c>
       <c r="AE66" s="1">
         <v>0</v>
@@ -4512,17 +4647,17 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66">
-        <v>6</v>
-      </c>
-      <c r="AH66">
-        <v>15</v>
+      <c r="AG66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="1">
+        <v>0</v>
       </c>
       <c r="AI66" s="1">
         <v>0</v>
       </c>
-      <c r="AJ66">
-        <v>12</v>
+      <c r="AJ66" s="1">
+        <v>0</v>
       </c>
       <c r="AK66" s="1">
         <v>0</v>
@@ -4541,7 +4676,9 @@
       <c r="W67" s="1"/>
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
+      <c r="Z67" s="1">
+        <v>0</v>
+      </c>
       <c r="AA67" s="1">
         <v>0</v>
       </c>
@@ -4589,7 +4726,9 @@
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
-      <c r="Z68" s="1"/>
+      <c r="Z68" s="1">
+        <v>0</v>
+      </c>
       <c r="AA68" s="1">
         <v>0</v>
       </c>
@@ -4631,13 +4770,16 @@
       <c r="A69" t="s">
         <v>95</v>
       </c>
+      <c r="S69" s="1"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
-      <c r="Z69" s="1"/>
+      <c r="Z69" s="1">
+        <v>0</v>
+      </c>
       <c r="AA69" s="1">
         <v>0</v>
       </c>
@@ -4679,13 +4821,16 @@
       <c r="A70" t="s">
         <v>96</v>
       </c>
+      <c r="S70" s="1"/>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
-      <c r="Z70" s="1"/>
+      <c r="Z70" s="1">
+        <v>0</v>
+      </c>
       <c r="AA70" s="1">
         <v>0</v>
       </c>
@@ -4727,13 +4872,16 @@
       <c r="A71" t="s">
         <v>97</v>
       </c>
+      <c r="S71" s="1"/>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
-      <c r="Z71" s="1"/>
+      <c r="Z71" s="1">
+        <v>0</v>
+      </c>
       <c r="AA71" s="1">
         <v>0</v>
       </c>
@@ -4782,7 +4930,9 @@
       <c r="W72" s="1"/>
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
-      <c r="Z72" s="1"/>
+      <c r="Z72" s="1">
+        <v>0</v>
+      </c>
       <c r="AA72" s="1">
         <v>0</v>
       </c>
@@ -4831,7 +4981,9 @@
       <c r="W73" s="1"/>
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
-      <c r="Z73" s="1"/>
+      <c r="Z73" s="1">
+        <v>0</v>
+      </c>
       <c r="AA73" s="1">
         <v>0</v>
       </c>
@@ -4873,6 +5025,7 @@
       <c r="A74" t="s">
         <v>100</v>
       </c>
+      <c r="R74" s="1"/>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
@@ -4880,7 +5033,9 @@
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
-      <c r="Z74" s="1"/>
+      <c r="Z74" s="1">
+        <v>0</v>
+      </c>
       <c r="AA74" s="1">
         <v>0</v>
       </c>
@@ -4922,6 +5077,7 @@
       <c r="A75" t="s">
         <v>101</v>
       </c>
+      <c r="R75" s="1"/>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
@@ -4929,7 +5085,9 @@
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
-      <c r="Z75" s="1"/>
+      <c r="Z75" s="1">
+        <v>0</v>
+      </c>
       <c r="AA75" s="1">
         <v>0</v>
       </c>
@@ -4971,6 +5129,8 @@
       <c r="A76" t="s">
         <v>102</v>
       </c>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -4978,7 +5138,9 @@
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
-      <c r="Z76" s="1"/>
+      <c r="Z76" s="1">
+        <v>0</v>
+      </c>
       <c r="AA76" s="1">
         <v>0</v>
       </c>
@@ -5020,6 +5182,7 @@
       <c r="A77" t="s">
         <v>103</v>
       </c>
+      <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
@@ -5028,7 +5191,9 @@
       <c r="W77" s="1"/>
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
-      <c r="Z77" s="1"/>
+      <c r="Z77" s="1">
+        <v>0</v>
+      </c>
       <c r="AA77" s="1">
         <v>0</v>
       </c>
@@ -5070,6 +5235,7 @@
       <c r="A78" t="s">
         <v>104</v>
       </c>
+      <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
@@ -5078,7 +5244,9 @@
       <c r="W78" s="1"/>
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
-      <c r="Z78" s="1"/>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
       <c r="AA78" s="1">
         <v>0</v>
       </c>
@@ -5129,7 +5297,9 @@
       <c r="W79" s="1"/>
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
-      <c r="Z79" s="1"/>
+      <c r="Z79" s="1">
+        <v>0</v>
+      </c>
       <c r="AA79" s="1">
         <v>0</v>
       </c>
@@ -5180,7 +5350,9 @@
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
-      <c r="Z80" s="1"/>
+      <c r="Z80" s="1">
+        <v>0</v>
+      </c>
       <c r="AA80" s="1">
         <v>0</v>
       </c>
@@ -5222,6 +5394,7 @@
       <c r="A81" t="s">
         <v>107</v>
       </c>
+      <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
@@ -5231,7 +5404,9 @@
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
-      <c r="Z81" s="1"/>
+      <c r="Z81" s="1">
+        <v>0</v>
+      </c>
       <c r="AA81" s="1">
         <v>0</v>
       </c>
@@ -5273,6 +5448,7 @@
       <c r="A82" t="s">
         <v>108</v>
       </c>
+      <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
@@ -5282,7 +5458,9 @@
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
-      <c r="Z82" s="1"/>
+      <c r="Z82" s="1">
+        <v>0</v>
+      </c>
       <c r="AA82" s="1">
         <v>0</v>
       </c>
@@ -5324,6 +5502,7 @@
       <c r="A83" t="s">
         <v>109</v>
       </c>
+      <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
@@ -5333,7 +5512,9 @@
       <c r="W83" s="1"/>
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
-      <c r="Z83" s="1"/>
+      <c r="Z83" s="1">
+        <v>0</v>
+      </c>
       <c r="AA83" s="1">
         <v>0</v>
       </c>
@@ -5385,7 +5566,9 @@
       <c r="W84" s="1"/>
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
-      <c r="Z84" s="1"/>
+      <c r="Z84" s="1">
+        <v>0</v>
+      </c>
       <c r="AA84" s="1">
         <v>0</v>
       </c>
@@ -5427,6 +5610,7 @@
       <c r="A85" t="s">
         <v>111</v>
       </c>
+      <c r="O85" s="1"/>
       <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
@@ -5437,7 +5621,9 @@
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
-      <c r="Z85" s="1"/>
+      <c r="Z85" s="1">
+        <v>0</v>
+      </c>
       <c r="AA85" s="1">
         <v>0</v>
       </c>
@@ -5479,6 +5665,7 @@
       <c r="A86" t="s">
         <v>112</v>
       </c>
+      <c r="O86" s="1"/>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
@@ -5489,7 +5676,9 @@
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
-      <c r="Z86" s="1"/>
+      <c r="Z86" s="1">
+        <v>0</v>
+      </c>
       <c r="AA86" s="1">
         <v>0</v>
       </c>
@@ -5531,6 +5720,7 @@
       <c r="A87" t="s">
         <v>113</v>
       </c>
+      <c r="O87" s="1"/>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
@@ -5541,7 +5731,9 @@
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
-      <c r="Z87" s="1"/>
+      <c r="Z87" s="1">
+        <v>0</v>
+      </c>
       <c r="AA87" s="1">
         <v>0</v>
       </c>
@@ -5594,7 +5786,9 @@
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
-      <c r="Z88" s="1"/>
+      <c r="Z88" s="1">
+        <v>0</v>
+      </c>
       <c r="AA88" s="1">
         <v>0</v>
       </c>
@@ -5647,7 +5841,9 @@
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
-      <c r="Z89" s="1"/>
+      <c r="Z89" s="1">
+        <v>0</v>
+      </c>
       <c r="AA89" s="1">
         <v>0</v>
       </c>
@@ -5689,6 +5885,7 @@
       <c r="A90" t="s">
         <v>116</v>
       </c>
+      <c r="N90" s="1"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -5700,7 +5897,9 @@
       <c r="W90" s="1"/>
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
-      <c r="Z90" s="1"/>
+      <c r="Z90" s="1">
+        <v>0</v>
+      </c>
       <c r="AA90" s="1">
         <v>0</v>
       </c>
@@ -5742,6 +5941,7 @@
       <c r="A91" t="s">
         <v>117</v>
       </c>
+      <c r="N91" s="1"/>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1"/>
@@ -5753,7 +5953,9 @@
       <c r="W91" s="1"/>
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
-      <c r="Z91" s="1"/>
+      <c r="Z91" s="1">
+        <v>0</v>
+      </c>
       <c r="AA91" s="1">
         <v>0</v>
       </c>
@@ -5795,6 +5997,7 @@
       <c r="A92" t="s">
         <v>118</v>
       </c>
+      <c r="N92" s="1"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -5806,7 +6009,9 @@
       <c r="W92" s="1"/>
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
-      <c r="Z92" s="1"/>
+      <c r="Z92" s="1">
+        <v>0</v>
+      </c>
       <c r="AA92" s="1">
         <v>0</v>
       </c>
@@ -5860,7 +6065,9 @@
       <c r="W93" s="1"/>
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
-      <c r="Z93" s="1"/>
+      <c r="Z93" s="1">
+        <v>0</v>
+      </c>
       <c r="AA93" s="1">
         <v>0</v>
       </c>
@@ -5914,7 +6121,9 @@
       <c r="W94" s="1"/>
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
-      <c r="Z94" s="1"/>
+      <c r="Z94" s="1">
+        <v>0</v>
+      </c>
       <c r="AA94" s="1">
         <v>0</v>
       </c>
@@ -5956,6 +6165,7 @@
       <c r="A95" t="s">
         <v>121</v>
       </c>
+      <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
@@ -5968,7 +6178,9 @@
       <c r="W95" s="1"/>
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
-      <c r="Z95" s="1"/>
+      <c r="Z95" s="1">
+        <v>0</v>
+      </c>
       <c r="AA95" s="1">
         <v>0</v>
       </c>
@@ -6010,6 +6222,7 @@
       <c r="A96" t="s">
         <v>122</v>
       </c>
+      <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
@@ -6022,7 +6235,9 @@
       <c r="W96" s="1"/>
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
-      <c r="Z96" s="1"/>
+      <c r="Z96" s="1">
+        <v>0</v>
+      </c>
       <c r="AA96" s="1">
         <v>0</v>
       </c>
@@ -6064,6 +6279,7 @@
       <c r="A97" t="s">
         <v>123</v>
       </c>
+      <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
@@ -6076,7 +6292,9 @@
       <c r="W97" s="1"/>
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
-      <c r="Z97" s="1"/>
+      <c r="Z97" s="1">
+        <v>0</v>
+      </c>
       <c r="AA97" s="1">
         <v>0</v>
       </c>
@@ -6131,7 +6349,9 @@
       <c r="W98" s="1"/>
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
-      <c r="Z98" s="1"/>
+      <c r="Z98" s="1">
+        <v>0</v>
+      </c>
       <c r="AA98" s="1">
         <v>0</v>
       </c>
@@ -6173,6 +6393,7 @@
       <c r="A99" t="s">
         <v>125</v>
       </c>
+      <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
@@ -6186,7 +6407,9 @@
       <c r="W99" s="1"/>
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
-      <c r="Z99" s="1"/>
+      <c r="Z99" s="1">
+        <v>0</v>
+      </c>
       <c r="AA99" s="1">
         <v>0</v>
       </c>
@@ -6228,6 +6451,7 @@
       <c r="A100" t="s">
         <v>126</v>
       </c>
+      <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
@@ -6241,7 +6465,9 @@
       <c r="W100" s="1"/>
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
-      <c r="Z100" s="1"/>
+      <c r="Z100" s="1">
+        <v>0</v>
+      </c>
       <c r="AA100" s="1">
         <v>0</v>
       </c>
@@ -6283,6 +6509,8 @@
       <c r="A101" t="s">
         <v>127</v>
       </c>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
@@ -6296,7 +6524,9 @@
       <c r="W101" s="1"/>
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
-      <c r="Z101" s="1"/>
+      <c r="Z101" s="1">
+        <v>0</v>
+      </c>
       <c r="AA101" s="1">
         <v>0</v>
       </c>
@@ -6338,6 +6568,7 @@
       <c r="A102" t="s">
         <v>128</v>
       </c>
+      <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
@@ -6352,7 +6583,9 @@
       <c r="W102" s="1"/>
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
-      <c r="Z102" s="1"/>
+      <c r="Z102" s="1">
+        <v>0</v>
+      </c>
       <c r="AA102" s="1">
         <v>0</v>
       </c>
@@ -6394,6 +6627,7 @@
       <c r="A103" t="s">
         <v>129</v>
       </c>
+      <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
@@ -6408,7 +6642,9 @@
       <c r="W103" s="1"/>
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
-      <c r="Z103" s="1"/>
+      <c r="Z103" s="1">
+        <v>0</v>
+      </c>
       <c r="AA103" s="1">
         <v>0</v>
       </c>
@@ -6450,6 +6686,7 @@
       <c r="A104" t="s">
         <v>130</v>
       </c>
+      <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
@@ -6465,7 +6702,9 @@
       <c r="W104" s="1"/>
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
-      <c r="Z104" s="1"/>
+      <c r="Z104" s="1">
+        <v>0</v>
+      </c>
       <c r="AA104" s="1">
         <v>0</v>
       </c>
@@ -6507,6 +6746,7 @@
       <c r="A105" t="s">
         <v>131</v>
       </c>
+      <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
@@ -6522,7 +6762,9 @@
       <c r="W105" s="1"/>
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
-      <c r="Z105" s="1"/>
+      <c r="Z105" s="1">
+        <v>0</v>
+      </c>
       <c r="AA105" s="1">
         <v>0</v>
       </c>
@@ -6564,6 +6806,7 @@
       <c r="A106" t="s">
         <v>132</v>
       </c>
+      <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
@@ -6579,7 +6822,9 @@
       <c r="W106" s="1"/>
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
-      <c r="Z106" s="1"/>
+      <c r="Z106" s="1">
+        <v>0</v>
+      </c>
       <c r="AA106" s="1">
         <v>0</v>
       </c>
@@ -6621,6 +6866,7 @@
       <c r="A107" t="s">
         <v>133</v>
       </c>
+      <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -6637,7 +6883,9 @@
       <c r="W107" s="1"/>
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
-      <c r="Z107" s="1"/>
+      <c r="Z107" s="1">
+        <v>0</v>
+      </c>
       <c r="AA107" s="1">
         <v>0</v>
       </c>
@@ -6679,6 +6927,7 @@
       <c r="A108" t="s">
         <v>134</v>
       </c>
+      <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -6695,7 +6944,9 @@
       <c r="W108" s="1"/>
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
-      <c r="Z108" s="1"/>
+      <c r="Z108" s="1">
+        <v>0</v>
+      </c>
       <c r="AA108" s="1">
         <v>0</v>
       </c>
@@ -6737,6 +6988,7 @@
       <c r="A109" t="s">
         <v>135</v>
       </c>
+      <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -6753,7 +7005,9 @@
       <c r="W109" s="1"/>
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
-      <c r="Z109" s="1"/>
+      <c r="Z109" s="1">
+        <v>0</v>
+      </c>
       <c r="AA109" s="1">
         <v>0</v>
       </c>
@@ -6795,6 +7049,7 @@
       <c r="A110" t="s">
         <v>136</v>
       </c>
+      <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
@@ -6812,7 +7067,9 @@
       <c r="W110" s="1"/>
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
-      <c r="Z110" s="1"/>
+      <c r="Z110" s="1">
+        <v>0</v>
+      </c>
       <c r="AA110" s="1">
         <v>0</v>
       </c>
@@ -6854,6 +7111,7 @@
       <c r="A111" t="s">
         <v>137</v>
       </c>
+      <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
@@ -6871,7 +7129,9 @@
       <c r="W111" s="1"/>
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
-      <c r="Z111" s="1"/>
+      <c r="Z111" s="1">
+        <v>0</v>
+      </c>
       <c r="AA111" s="1">
         <v>0</v>
       </c>
@@ -6913,6 +7173,8 @@
       <c r="A112" t="s">
         <v>138</v>
       </c>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
@@ -6930,7 +7192,9 @@
       <c r="W112" s="1"/>
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
-      <c r="Z112" s="1"/>
+      <c r="Z112" s="1">
+        <v>0</v>
+      </c>
       <c r="AA112" s="1">
         <v>0</v>
       </c>
@@ -6972,6 +7236,7 @@
       <c r="A113" t="s">
         <v>139</v>
       </c>
+      <c r="G113" s="1"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6990,7 +7255,9 @@
       <c r="W113" s="1"/>
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
-      <c r="Z113" s="1"/>
+      <c r="Z113" s="1">
+        <v>0</v>
+      </c>
       <c r="AA113" s="1">
         <v>0</v>
       </c>
@@ -7032,6 +7299,7 @@
       <c r="A114" t="s">
         <v>140</v>
       </c>
+      <c r="G114" s="1"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -7050,7 +7318,9 @@
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
-      <c r="Z114" s="1"/>
+      <c r="Z114" s="1">
+        <v>0</v>
+      </c>
       <c r="AA114" s="1">
         <v>0</v>
       </c>
@@ -7092,6 +7362,7 @@
       <c r="A115" t="s">
         <v>141</v>
       </c>
+      <c r="F115" s="1"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
@@ -7111,7 +7382,9 @@
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
-      <c r="Z115" s="1"/>
+      <c r="Z115" s="1">
+        <v>0</v>
+      </c>
       <c r="AA115" s="1">
         <v>0</v>
       </c>
@@ -7153,6 +7426,7 @@
       <c r="A116" t="s">
         <v>142</v>
       </c>
+      <c r="F116" s="1"/>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
@@ -7172,7 +7446,9 @@
       <c r="W116" s="1"/>
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
-      <c r="Z116" s="1"/>
+      <c r="Z116" s="1">
+        <v>0</v>
+      </c>
       <c r="AA116" s="1">
         <v>0</v>
       </c>
@@ -7214,6 +7490,7 @@
       <c r="A117" t="s">
         <v>143</v>
       </c>
+      <c r="F117" s="1"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
@@ -7233,7 +7510,9 @@
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
-      <c r="Z117" s="1"/>
+      <c r="Z117" s="1">
+        <v>0</v>
+      </c>
       <c r="AA117" s="1">
         <v>0</v>
       </c>
@@ -7275,6 +7554,7 @@
       <c r="A118" t="s">
         <v>144</v>
       </c>
+      <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
@@ -7295,7 +7575,9 @@
       <c r="W118" s="1"/>
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
-      <c r="Z118" s="1"/>
+      <c r="Z118" s="1">
+        <v>0</v>
+      </c>
       <c r="AA118" s="1">
         <v>0</v>
       </c>
@@ -7337,6 +7619,7 @@
       <c r="A119" t="s">
         <v>145</v>
       </c>
+      <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
@@ -7357,7 +7640,9 @@
       <c r="W119" s="1"/>
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
-      <c r="Z119" s="1"/>
+      <c r="Z119" s="1">
+        <v>0</v>
+      </c>
       <c r="AA119" s="1">
         <v>0</v>
       </c>
@@ -7399,6 +7684,7 @@
       <c r="A120" t="s">
         <v>146</v>
       </c>
+      <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
@@ -7419,7 +7705,9 @@
       <c r="W120" s="1"/>
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
-      <c r="Z120" s="1"/>
+      <c r="Z120" s="1">
+        <v>0</v>
+      </c>
       <c r="AA120" s="1">
         <v>0</v>
       </c>
@@ -7461,6 +7749,7 @@
       <c r="A121" t="s">
         <v>147</v>
       </c>
+      <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
@@ -7482,7 +7771,9 @@
       <c r="W121" s="1"/>
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
-      <c r="Z121" s="1"/>
+      <c r="Z121" s="1">
+        <v>0</v>
+      </c>
       <c r="AA121" s="1">
         <v>0</v>
       </c>
@@ -7517,196 +7808,6 @@
         <v>0</v>
       </c>
       <c r="AL121" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>148</v>
-      </c>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="1"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1"/>
-      <c r="P122" s="1"/>
-      <c r="Q122" s="1"/>
-      <c r="R122" s="1"/>
-      <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
-      <c r="U122" s="1"/>
-      <c r="V122" s="1"/>
-      <c r="W122" s="1"/>
-      <c r="X122" s="1"/>
-      <c r="Y122" s="1"/>
-      <c r="Z122" s="1"/>
-      <c r="AA122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL122" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>149</v>
-      </c>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="1"/>
-      <c r="N123" s="1"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1"/>
-      <c r="Q123" s="1"/>
-      <c r="R123" s="1"/>
-      <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
-      <c r="U123" s="1"/>
-      <c r="V123" s="1"/>
-      <c r="W123" s="1"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="1"/>
-      <c r="Z123" s="1"/>
-      <c r="AA123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>150</v>
-      </c>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
-      <c r="K124" s="1"/>
-      <c r="L124" s="1"/>
-      <c r="M124" s="1"/>
-      <c r="N124" s="1"/>
-      <c r="O124" s="1"/>
-      <c r="P124" s="1"/>
-      <c r="Q124" s="1"/>
-      <c r="R124" s="1"/>
-      <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
-      <c r="U124" s="1"/>
-      <c r="V124" s="1"/>
-      <c r="W124" s="1"/>
-      <c r="X124" s="1"/>
-      <c r="Y124" s="1"/>
-      <c r="Z124" s="1"/>
-      <c r="AA124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL124" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8366,7 +8467,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -8480,7 +8581,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -8537,7 +8638,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -8594,7 +8695,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -8651,7 +8752,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -9458,7 +9559,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -9578,7 +9679,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -9638,7 +9739,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -9698,7 +9799,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -9758,7 +9859,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -10866,7 +10967,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -10986,7 +11087,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -11046,7 +11147,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -12214,7 +12315,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <f>SUM(C19:C19:S19)</f>
@@ -12944,7 +13045,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -13229,7 +13330,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -13343,7 +13444,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -13571,7 +13672,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -13685,7 +13786,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -13742,7 +13843,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -13799,7 +13900,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
@@ -13856,7 +13957,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
@@ -13913,7 +14014,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
@@ -13970,7 +14071,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
@@ -14063,7 +14164,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -14118,17 +14219,17 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -14138,12 +14239,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -14153,22 +14254,22 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -14191,7 +14292,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -14261,27 +14362,27 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -14291,12 +14392,12 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -14306,12 +14407,12 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -14334,7 +14435,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -14409,37 +14510,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -14449,22 +14550,22 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14492,12 +14593,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -14512,12 +14613,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -14527,7 +14628,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -14537,7 +14638,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -14552,7 +14653,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -14572,12 +14673,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -14587,27 +14688,27 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -14630,7 +14731,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -14645,12 +14746,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -14660,12 +14761,12 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -14675,7 +14776,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -14685,12 +14786,12 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -14700,7 +14801,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -14710,7 +14811,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -14725,7 +14826,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -14735,7 +14836,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -14893,7 +14994,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -14908,7 +15009,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -14918,7 +15019,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -14928,12 +15029,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -14943,7 +15044,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -14953,7 +15054,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -14963,52 +15064,52 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -15031,12 +15132,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -15046,7 +15147,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -15061,12 +15162,12 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -15081,32 +15182,32 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -15121,12 +15222,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -15136,32 +15237,32 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -15184,7 +15285,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -15199,12 +15300,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -15214,7 +15315,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -15224,12 +15325,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -15239,27 +15340,27 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -15269,12 +15370,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -15289,37 +15390,37 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -15342,12 +15443,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -15357,7 +15458,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -15377,27 +15478,27 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -15407,57 +15508,57 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -15485,12 +15586,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -15500,7 +15601,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -15510,12 +15611,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -15530,72 +15631,72 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -15618,32 +15719,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -15658,17 +15759,17 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -15678,57 +15779,57 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -15751,17 +15852,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -15771,7 +15872,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -15781,47 +15882,47 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -15831,27 +15932,27 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -15874,27 +15975,27 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -15904,22 +16005,22 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -15929,17 +16030,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -15949,47 +16050,47 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -16012,17 +16113,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -16032,32 +16133,32 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -16067,62 +16168,62 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -16145,12 +16246,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -16160,87 +16261,87 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -16394,57 +16495,57 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -16454,42 +16555,42 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -16512,77 +16613,77 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -16592,37 +16693,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -16645,77 +16746,77 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -16725,27 +16826,27 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -16768,112 +16869,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -16896,112 +16997,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -17024,122 +17125,122 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -17163,107 +17264,107 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -17286,112 +17387,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -17641,7 +17742,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -17723,7 +17824,7 @@
         <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
         <v>27</v>
@@ -18055,7 +18156,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -18169,7 +18270,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -18248,7 +18349,7 @@
         <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
         <v>27</v>
@@ -18287,7 +18388,7 @@
         <v>32</v>
       </c>
       <c r="Q1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -18598,7 +18699,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -18718,7 +18819,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -18778,7 +18879,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -18863,7 +18964,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>32</v>
@@ -19306,7 +19407,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -19420,7 +19521,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -19477,7 +19578,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -19559,7 +19660,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>27</v>
@@ -19595,7 +19696,7 @@
         <v>29</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -20146,7 +20247,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -20266,7 +20367,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -20326,7 +20427,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -20413,7 +20514,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>27</v>
@@ -20449,7 +20550,7 @@
         <v>38</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -20970,7 +21071,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -21084,7 +21185,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -21141,7 +21242,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>

--- a/Data_Files/Driver_Experience.xlsx
+++ b/Data_Files/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32D8CF9-DE86-42D7-B5CA-227A7829E748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4C3F84-78BA-4302-80F3-FED4D1364A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="60" windowWidth="16410" windowHeight="15480" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="8" activeTab="14" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -519,6 +519,15 @@
   </si>
   <si>
     <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Bahrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy </t>
+  </si>
+  <si>
+    <t>China</t>
   </si>
 </sst>
 </file>
@@ -14133,143 +14142,687 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E80DB57-1D34-4995-8AA7-BD186A2BDBE8}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R1" t="s">
+        <v>152</v>
+      </c>
+      <c r="S1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <f>SUM(C2:T2)</f>
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <f t="shared" ref="B3:B26" si="0">SUM(C3:T3)</f>
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
